--- a/stories/arbres/TREE-DIF-001.xlsx
+++ b/stories/arbres/TREE-DIF-001.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1163,7 +1180,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Aujourd'hui, Tom est au bord de la mer. Maman est là. Papa n'est pas loin. Tom voit des enfants. Certains sont plus grands. Certains sont plus petits. Les tailles sont différentes. Maman dit : on invite. On joue ensemble. On peut jouer ensemble.</t>
+          <t>Aujourd'hui, Tom est au bord de la mer. Maman est là. Papa n'est pas loin. Tom voit des enfants. Certains sont plus grands. Certains sont plus petits. Les tailles sont différentes. On invite. On joue ensemble. On peut jouer ensemble.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1301,6 +1318,12 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Aujourd'hui, Tom est au bord de la mer. Maman est là. Papa n'est pas loin. Tom voit des enfants. Certains sont plus grands. Certains sont plus petits. Les tailles sont différentes.
+maman|On invite. On joue ensemble. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1510,11 @@
         <v>12</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1649,6 +1677,11 @@
         <v>12</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Après la mer, Tom rentre. Il va dans la cuisine. L'eau coule, tout petit bruit. Un copain plus grand lave un coquillage. Tom l'invite. Ils jouent ensemble. Les tailles sont différentes. Maman sourit. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1825,6 +1858,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|On joue ensemble ?</t>
         </is>
       </c>
     </row>
@@ -1993,6 +2031,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. On joue ensemble. Tom respire. Maman est là. Les tailles sont différentes. On joue ensemble. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2179,6 +2222,11 @@
         <v>12</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2341,6 +2389,11 @@
         <v>12</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Tom pose le ballon rouge près de l'évier. Un copain plus grand le fait rouler, tout doux. Maman montre le geste, lentement. Les tailles sont différentes. On joue ensemble. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2531,6 +2584,11 @@
           <t>prompt réécrit pour coller aux options</t>
         </is>
       </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2555,7 +2613,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Tom a choisi la cuisine. Puis le ballon rouge. Puis Tom. Une pomme brille un peu. Tom dit : j'ai appris. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Tom dit merci à maman.</t>
+          <t>Tom a choisi la cuisine. Puis le ballon rouge. Puis Tom. Une pomme brille un peu. J'ai appris. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Tom dit merci à maman.</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -2693,6 +2751,13 @@
         <v>12</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Tom a choisi la cuisine. Puis le ballon rouge. Puis Tom. Une pomme brille un peu.
+enfant-m|J'ai appris.
+narrateur|Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Tom dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2855,6 +2920,11 @@
         <v>12</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3017,6 +3087,11 @@
         <v>12</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Tom s'arrête près de Léa. le ballon rouge est rangé. Un ruban reste dans la poche. Tom essuie ses mains. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Tom dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3179,6 +3254,11 @@
         <v>12</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3341,6 +3421,11 @@
         <v>12</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Tom se souvient de la cuisine. Et de le ballon rouge. Et de Sami. Un crochet tient bien le manteau. Tom range encore un peu, près de maman. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Tom dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3503,6 +3588,11 @@
         <v>12</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3527,7 +3617,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Tom remplit le seau bleu. Un copain plus petit tient l'anse avec lui. Maman dit : je suis là. Les tailles sont différentes. On joue ensemble. On peut jouer ensemble.</t>
+          <t>Tom remplit le seau bleu. Un copain plus petit tient l'anse avec lui. Je suis là. Les tailles sont différentes. On joue ensemble. On peut jouer ensemble.</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -3665,6 +3755,13 @@
         <v>12</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Tom remplit le seau bleu. Un copain plus petit tient l'anse avec lui.
+maman|Je suis là.
+narrateur|Les tailles sont différentes. On joue ensemble. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3853,6 +3950,11 @@
       <c r="AV17" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -4017,6 +4119,11 @@
         <v>12</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Avec Tom. Après le seau bleu. Près de la cuisine. Tom s'arrête. L'eau coule, tout petit bruit. Tom répète tout bas le geste. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Tom dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4179,6 +4286,11 @@
         <v>12</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4341,6 +4453,11 @@
         <v>12</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Tom range le seau bleu. Léa reste près de la cuisine. Ça sent le pain chaud. Tom montre Léa à maman. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Tom dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4503,6 +4620,11 @@
         <v>12</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4665,6 +4787,11 @@
         <v>12</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Sami est là. le seau bleu aussi. la cuisine reste dans le souvenir. Un chat miaule une fois. Tom pose sa tête un moment. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Tom dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4827,6 +4954,11 @@
         <v>12</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4989,6 +5121,11 @@
         <v>12</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Tom pose le doudou sur une chaise sèche. Un copain d'une autre taille le caresse. Maman reste tout près. Les tailles sont différentes. On joue ensemble. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5177,6 +5314,11 @@
       <c r="AV25" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -5341,6 +5483,11 @@
         <v>12</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint Tom. le doudou est rangé. la cuisine est fini. Il y a des miettes sur la table. Tom pose le doudou à sa place. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Tom dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5503,6 +5650,11 @@
         <v>12</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5665,6 +5817,11 @@
         <v>12</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Près de Léa. Tom pose le doudou. la cuisine est derrière. La lumière est claire. Tom caresse le doudou. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Tom dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5827,6 +5984,11 @@
         <v>12</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5989,6 +6151,11 @@
         <v>12</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Tom montre Sami. Maman a vu la cuisine. Et le doudou. Un vélo passe au loin. Tom range la cuisine dans sa tête, comme un souvenir. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Tom dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6151,6 +6318,11 @@
         <v>12</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6313,6 +6485,11 @@
         <v>12</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Après la mer, Tom va dans le jardin. L'herbe est tiède. Un copain plus petit tient un arrosoir. Tom l'invite. Ils versent l'eau, tout doux. Ils jouent ensemble. Les tailles sont différentes. Maman est là. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6493,6 +6670,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Les tailles sont différentes. On fait quoi ?</t>
         </is>
       </c>
     </row>
@@ -6661,6 +6843,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. On joue ensemble. Tom retient le geste. Maman sourit. Les tailles sont différentes. On joue ensemble. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6847,6 +7034,11 @@
         <v>12</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -6871,7 +7063,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Tom fait rouler le ballon rouge dans l'herbe. Un copain plus grand le rattrape. Maman dit : je suis là. Les tailles sont différentes. On joue ensemble. On peut jouer ensemble.</t>
+          <t>Tom fait rouler le ballon rouge dans l'herbe. Un copain plus grand le rattrape. Je suis là. Les tailles sont différentes. On joue ensemble. On peut jouer ensemble.</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -7009,6 +7201,13 @@
         <v>12</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Tom fait rouler le ballon rouge dans l'herbe. Un copain plus grand le rattrape.
+maman|Je suis là.
+narrateur|Les tailles sont différentes. On joue ensemble. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7197,6 +7396,11 @@
       <c r="AV37" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -7361,6 +7565,11 @@
         <v>12</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Tom a choisi le jardin. Puis le ballon rouge. Puis Tom. Un linge sèche à l'air. Tom tend Tom à papa. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Tom dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7523,6 +7732,11 @@
         <v>12</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7685,6 +7899,11 @@
         <v>12</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Tom s'arrête près de Léa. le ballon rouge est rangé. Le vent est doux. Papa n'est pas loin. Tom les rejoint. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Tom dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7847,6 +8066,11 @@
         <v>12</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8009,6 +8233,11 @@
         <v>12</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Tom se souvient de le jardin. Et de le ballon rouge. Et de Sami. On attend son tour. Tom marche près de maman. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Tom dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8171,6 +8400,11 @@
         <v>12</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8333,6 +8567,11 @@
         <v>12</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Tom pose le seau bleu sous le robinet du jardin. Un copain plus petit rit un peu. Maman reste tout près. Les tailles sont différentes. On joue ensemble. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8521,6 +8760,11 @@
       <c r="AV45" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -8685,6 +8929,11 @@
         <v>12</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Avec Tom. Après le seau bleu. Près de le jardin. Tom s'arrête. Un panier est posé sur le banc. Tom range la tasse. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Tom dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8847,6 +9096,11 @@
         <v>12</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9009,6 +9263,11 @@
         <v>12</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Tom range le seau bleu. Léa reste près de le jardin. Un ballon s'immobilise. Tom chuchote : c'est fini. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Tom dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9171,6 +9430,11 @@
         <v>12</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9333,6 +9597,11 @@
         <v>12</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Sami est là. le seau bleu aussi. le jardin reste dans le souvenir. Une feuille tombe. Tom ferme le sac. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Tom dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9495,6 +9764,11 @@
         <v>12</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9657,6 +9931,11 @@
         <v>12</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Tom assoit le doudou sous un linge. Un copain d'une autre taille l'abrite. Maman montre le geste, lentement. Les tailles sont différentes. On joue ensemble. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9845,6 +10124,11 @@
       <c r="AV53" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -10009,6 +10293,11 @@
         <v>12</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint Tom. le doudou est rangé. le jardin est fini. Une chaussette est encore sablée. Tom ferme la porte, tout doux. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Tom dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10171,6 +10460,11 @@
         <v>12</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10333,6 +10627,11 @@
         <v>12</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Près de Léa. Tom pose le doudou. le jardin est derrière. On écoute jusqu'au bout. Tom écoute maman encore une fois. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Tom dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10495,6 +10794,11 @@
         <v>12</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10657,6 +10961,11 @@
         <v>12</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Tom montre Sami. Maman a vu le jardin. Et le doudou. On range un objet. Tom plie un pull. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Tom dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10819,6 +11128,11 @@
         <v>12</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10981,6 +11295,11 @@
         <v>12</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Après la mer, Tom va dans la chambre. La couverture est douce. Un copain d'une autre taille pose un galet. Tom l'invite. Ils font un bateau avec l'oreiller. Ils jouent ensemble. Les tailles sont différentes. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11157,6 +11476,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|On invite, et on joue ensemble ?</t>
         </is>
       </c>
     </row>
@@ -11325,6 +11649,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. On joue ensemble. Tom hoche la tête. On continue, avec maman. Les tailles sont différentes. On joue ensemble. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11511,6 +11840,11 @@
         <v>12</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11673,6 +12007,11 @@
         <v>12</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Tom fait un bateau : le ballon rouge est le phare. Un copain plus grand tient l'oreiller. Maman reste tout près. Les tailles sont différentes. On joue ensemble. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11861,6 +12200,11 @@
       <c r="AV65" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -12025,6 +12369,11 @@
         <v>12</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Tom a choisi la chambre. Puis le ballon rouge. Puis Tom. On entend un oiseau. Tom raccroche un linge. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Tom dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12187,6 +12536,11 @@
         <v>12</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12349,6 +12703,11 @@
         <v>12</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Tom s'arrête près de Léa. le ballon rouge est rangé. On rit un peu. Tom dit merci à maman. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Tom dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12511,6 +12870,11 @@
         <v>12</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12673,6 +13037,11 @@
         <v>12</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Tom se souvient de la chambre. Et de le ballon rouge. Et de Sami. On dit merci. Tom souffle, puis sourit à maman. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Tom dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12835,6 +13204,11 @@
         <v>12</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -12997,6 +13371,11 @@
         <v>12</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Tom cache le seau bleu derrière le lit. Un copain plus petit le retrouve. Maman montre le geste, lentement. Les tailles sont différentes. On joue ensemble. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13185,6 +13564,11 @@
       <c r="AV73" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -13349,6 +13733,11 @@
         <v>12</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Avec Tom. Après le seau bleu. Près de la chambre. Tom s'arrête. Les chaussures font toc toc. Tom serre la main de maman. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Tom dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13511,6 +13900,11 @@
         <v>12</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13673,6 +14067,11 @@
         <v>12</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Tom range le seau bleu. Léa reste près de la chambre. On souffle doucement. Tom sourit. Maman sourit aussi. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Tom dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13835,6 +14234,11 @@
         <v>12</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -13997,6 +14401,11 @@
         <v>12</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Sami est là. le seau bleu aussi. la chambre reste dans le souvenir. Le savon sent bon. Tom boit une gorgée d'eau. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Tom dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14159,6 +14568,11 @@
         <v>12</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14183,7 +14597,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Tom calce le doudou sous la couverture. Un copain d'une autre taille chuchote. Maman dit : je suis là. Les tailles sont différentes. On joue ensemble. On peut jouer ensemble.</t>
+          <t>Tom calce le doudou sous la couverture. Un copain d'une autre taille chuchote. Je suis là. Les tailles sont différentes. On joue ensemble. On peut jouer ensemble.</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -14321,6 +14735,13 @@
         <v>12</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Tom calce le doudou sous la couverture. Un copain d'une autre taille chuchote.
+maman|Je suis là.
+narrateur|Les tailles sont différentes. On joue ensemble. On peut jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14509,6 +14930,11 @@
       <c r="AV81" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -14673,6 +15099,11 @@
         <v>12</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint Tom. le doudou est rangé. la chambre est fini. Une cloche tinte, tout loin. Tom enfile ses chaussons. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Tom dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14835,6 +15266,11 @@
         <v>12</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -14997,6 +15433,11 @@
         <v>12</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Près de Léa. Tom pose le doudou. la chambre est derrière. On se tient la main. Tom prend la main de maman. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Tom dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15159,6 +15600,11 @@
         <v>12</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15321,6 +15767,11 @@
         <v>12</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Tom montre Sami. Maman a vu la chambre. Et le doudou. La couverture est douce. Tom s'assoit près de maman. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Tom dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15483,6 +15934,11 @@
         <v>12</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15501,7 +15957,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15574,6 +16030,13 @@
       <c r="A10" t="inlineStr">
         <is>
           <t>ch3C3: prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-DIF-001.xlsx
+++ b/stories/arbres/TREE-DIF-001.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1324,6 +1329,7 @@
 maman|On invite. On joue ensemble. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1515,6 +1521,7 @@
           <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1682,6 +1689,7 @@
           <t>narrateur|Après la mer, Tom rentre. Il va dans la cuisine. L'eau coule, tout petit bruit. Un copain plus grand lave un coquillage. Tom l'invite. Ils jouent ensemble. Les tailles sont différentes. Maman sourit. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1865,6 +1873,7 @@
           <t>narrateur|On joue ensemble ?</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2036,6 +2045,7 @@
           <t>narrateur|Oui. On joue ensemble. Tom respire. Maman est là. Les tailles sont différentes. On joue ensemble. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2227,6 +2237,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2394,6 +2405,7 @@
           <t>narrateur|Tom pose le ballon rouge près de l'évier. Un copain plus grand le fait rouler, tout doux. Maman montre le geste, lentement. Les tailles sont différentes. On joue ensemble. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2589,6 +2601,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2758,6 +2771,7 @@
 narrateur|Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Tom dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2925,6 +2939,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3092,6 +3107,7 @@
           <t>narrateur|Tom s'arrête près de Léa. le ballon rouge est rangé. Un ruban reste dans la poche. Tom essuie ses mains. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Tom dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3259,6 +3275,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3426,6 +3443,7 @@
           <t>narrateur|Tom se souvient de la cuisine. Et de le ballon rouge. Et de Sami. Un crochet tient bien le manteau. Tom range encore un peu, près de maman. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Tom dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3593,6 +3611,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3762,6 +3781,7 @@
 narrateur|Les tailles sont différentes. On joue ensemble. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3957,6 +3977,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4124,6 +4145,7 @@
           <t>narrateur|Avec Tom. Après le seau bleu. Près de la cuisine. Tom s'arrête. L'eau coule, tout petit bruit. Tom répète tout bas le geste. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Tom dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4291,6 +4313,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4458,6 +4481,7 @@
           <t>narrateur|Tom range le seau bleu. Léa reste près de la cuisine. Ça sent le pain chaud. Tom montre Léa à maman. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Tom dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4625,6 +4649,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4792,6 +4817,7 @@
           <t>narrateur|Sami est là. le seau bleu aussi. la cuisine reste dans le souvenir. Un chat miaule une fois. Tom pose sa tête un moment. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Tom dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4959,6 +4985,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5126,6 +5153,7 @@
           <t>narrateur|Tom pose le doudou sur une chaise sèche. Un copain d'une autre taille le caresse. Maman reste tout près. Les tailles sont différentes. On joue ensemble. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5321,6 +5349,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5488,6 +5517,7 @@
           <t>narrateur|Tom rejoint Tom. le doudou est rangé. la cuisine est fini. Il y a des miettes sur la table. Tom pose le doudou à sa place. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Tom dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5655,6 +5685,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5822,6 +5853,7 @@
           <t>narrateur|Près de Léa. Tom pose le doudou. la cuisine est derrière. La lumière est claire. Tom caresse le doudou. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Tom dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5989,6 +6021,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6156,6 +6189,7 @@
           <t>narrateur|Tom montre Sami. Maman a vu la cuisine. Et le doudou. Un vélo passe au loin. Tom range la cuisine dans sa tête, comme un souvenir. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Tom dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6323,6 +6357,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6490,6 +6525,7 @@
           <t>narrateur|Après la mer, Tom va dans le jardin. L'herbe est tiède. Un copain plus petit tient un arrosoir. Tom l'invite. Ils versent l'eau, tout doux. Ils jouent ensemble. Les tailles sont différentes. Maman est là. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6677,6 +6713,7 @@
           <t>narrateur|Les tailles sont différentes. On fait quoi ?</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6848,6 +6885,7 @@
           <t>narrateur|Oui. On joue ensemble. Tom retient le geste. Maman sourit. Les tailles sont différentes. On joue ensemble. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7039,6 +7077,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7208,6 +7247,7 @@
 narrateur|Les tailles sont différentes. On joue ensemble. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7403,6 +7443,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7570,6 +7611,7 @@
           <t>narrateur|Tom a choisi le jardin. Puis le ballon rouge. Puis Tom. Un linge sèche à l'air. Tom tend Tom à papa. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Tom dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7737,6 +7779,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7904,6 +7947,7 @@
           <t>narrateur|Tom s'arrête près de Léa. le ballon rouge est rangé. Le vent est doux. Papa n'est pas loin. Tom les rejoint. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Tom dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8071,6 +8115,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8238,6 +8283,7 @@
           <t>narrateur|Tom se souvient de le jardin. Et de le ballon rouge. Et de Sami. On attend son tour. Tom marche près de maman. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Tom dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8405,6 +8451,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8572,6 +8619,7 @@
           <t>narrateur|Tom pose le seau bleu sous le robinet du jardin. Un copain plus petit rit un peu. Maman reste tout près. Les tailles sont différentes. On joue ensemble. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8767,6 +8815,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8934,6 +8983,7 @@
           <t>narrateur|Avec Tom. Après le seau bleu. Près de le jardin. Tom s'arrête. Un panier est posé sur le banc. Tom range la tasse. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Tom dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9101,6 +9151,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9268,6 +9319,7 @@
           <t>narrateur|Tom range le seau bleu. Léa reste près de le jardin. Un ballon s'immobilise. Tom chuchote : c'est fini. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Tom dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9435,6 +9487,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9602,6 +9655,7 @@
           <t>narrateur|Sami est là. le seau bleu aussi. le jardin reste dans le souvenir. Une feuille tombe. Tom ferme le sac. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Tom dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9769,6 +9823,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9936,6 +9991,7 @@
           <t>narrateur|Tom assoit le doudou sous un linge. Un copain d'une autre taille l'abrite. Maman montre le geste, lentement. Les tailles sont différentes. On joue ensemble. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10131,6 +10187,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10298,6 +10355,7 @@
           <t>narrateur|Tom rejoint Tom. le doudou est rangé. le jardin est fini. Une chaussette est encore sablée. Tom ferme la porte, tout doux. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Tom dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10465,6 +10523,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10632,6 +10691,7 @@
           <t>narrateur|Près de Léa. Tom pose le doudou. le jardin est derrière. On écoute jusqu'au bout. Tom écoute maman encore une fois. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Tom dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10799,6 +10859,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10966,6 +11027,7 @@
           <t>narrateur|Tom montre Sami. Maman a vu le jardin. Et le doudou. On range un objet. Tom plie un pull. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Tom dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11133,6 +11195,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11300,6 +11363,7 @@
           <t>narrateur|Après la mer, Tom va dans la chambre. La couverture est douce. Un copain d'une autre taille pose un galet. Tom l'invite. Ils font un bateau avec l'oreiller. Ils jouent ensemble. Les tailles sont différentes. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11483,6 +11547,7 @@
           <t>narrateur|On invite, et on joue ensemble ?</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11654,6 +11719,7 @@
           <t>narrateur|Oui. On joue ensemble. Tom hoche la tête. On continue, avec maman. Les tailles sont différentes. On joue ensemble. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11845,6 +11911,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -12012,6 +12079,7 @@
           <t>narrateur|Tom fait un bateau : le ballon rouge est le phare. Un copain plus grand tient l'oreiller. Maman reste tout près. Les tailles sont différentes. On joue ensemble. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12207,6 +12275,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12374,6 +12443,7 @@
           <t>narrateur|Tom a choisi la chambre. Puis le ballon rouge. Puis Tom. On entend un oiseau. Tom raccroche un linge. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Tom dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12541,6 +12611,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12708,6 +12779,7 @@
           <t>narrateur|Tom s'arrête près de Léa. le ballon rouge est rangé. On rit un peu. Tom dit merci à maman. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Tom dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12875,6 +12947,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13042,6 +13115,7 @@
           <t>narrateur|Tom se souvient de la chambre. Et de le ballon rouge. Et de Sami. On dit merci. Tom souffle, puis sourit à maman. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Tom dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13209,6 +13283,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13376,6 +13451,7 @@
           <t>narrateur|Tom cache le seau bleu derrière le lit. Un copain plus petit le retrouve. Maman montre le geste, lentement. Les tailles sont différentes. On joue ensemble. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13571,6 +13647,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13738,6 +13815,7 @@
           <t>narrateur|Avec Tom. Après le seau bleu. Près de la chambre. Tom s'arrête. Les chaussures font toc toc. Tom serre la main de maman. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Tom dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13905,6 +13983,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14072,6 +14151,7 @@
           <t>narrateur|Tom range le seau bleu. Léa reste près de la chambre. On souffle doucement. Tom sourit. Maman sourit aussi. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Tom dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14239,6 +14319,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14406,6 +14487,7 @@
           <t>narrateur|Sami est là. le seau bleu aussi. la chambre reste dans le souvenir. Le savon sent bon. Tom boit une gorgée d'eau. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Tom dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14573,6 +14655,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14742,6 +14825,7 @@
 narrateur|Les tailles sont différentes. On joue ensemble. On peut jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14937,6 +15021,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15104,6 +15189,7 @@
           <t>narrateur|Tom rejoint Tom. le doudou est rangé. la chambre est fini. Une cloche tinte, tout loin. Tom enfile ses chaussons. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Tom dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15271,6 +15357,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15438,6 +15525,7 @@
           <t>narrateur|Près de Léa. Tom pose le doudou. la chambre est derrière. On se tient la main. Tom prend la main de maman. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Tom dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15605,6 +15693,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15772,6 +15861,7 @@
           <t>narrateur|Tom montre Sami. Maman a vu la chambre. Et le doudou. La couverture est douce. Tom s'assoit près de maman. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Tom dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15939,6 +16029,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15957,7 +16048,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16037,6 +16128,20 @@
       <c r="A11" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -16051,7 +16156,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16238,6 +16343,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/TREE-DIF-001.xlsx
+++ b/stories/arbres/TREE-DIF-001.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -552,7 +552,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Plus petit ou plus grand — au bord de la mer</t>
+          <t>Les empreintes et le coquillage d'Aniss</t>
         </is>
       </c>
     </row>
@@ -843,6 +843,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Sur le sable, deux empreintes : une petite, une plus grande. Aniss invite Sarah. Les tailles sont différentes. Ils jouent ensemble, jusque dans la maison, avec un souvenir de mer.</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1197,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Aujourd'hui, Tom est au bord de la mer. Maman est là. Papa n'est pas loin. Tom voit des enfants. Certains sont plus grands. Certains sont plus petits. Les tailles sont différentes. On invite. On joue ensemble. On peut jouer ensemble.</t>
+          <t>Le vent secoue une serviette, tout blanche. Du sable tombe, en petite pluie. Un coquillage a un trou, tout rond. La mer chante, tout loin, tout bas. Le sable mouillé colle aux orteils. Papa a retroussé son pantalon. Maman secoue encore la serviette. Deux empreintes brillent, dans le sable. Une petite. Une plus grande. Tu as vu les traces ? Elles sont différentes. Oui. Les tailles sont différentes. En ce moment, Aniss ramasse le coquillage. Le trou laisse passer le ciel. Sarah arrive, plus grande. Ses pieds font des traces plus longues. Tu viens jouer ? Oui. On invite. On joue ensemble. Bravo, Aniss. Tu as invité. Ils posent le coquillage, tout doux. Le vent pousse encore la serviette.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1325,11 +1337,39 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Aujourd'hui, Tom est au bord de la mer. Maman est là. Papa n'est pas loin. Tom voit des enfants. Certains sont plus grands. Certains sont plus petits. Les tailles sont différentes.
-maman|On invite. On joue ensemble. On peut jouer ensemble.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|Le vent secoue une serviette, tout blanche.
+narrateur|Du sable tombe, en petite pluie.
+narrateur|Un coquillage a un trou, tout rond.
+narrateur|La mer chante, tout loin, tout bas.
+narrateur|Le sable mouillé colle aux orteils.
+narrateur|Papa a retroussé son pantalon.
+narrateur|Maman secoue encore la serviette.
+narrateur|Deux empreintes brillent, dans le sable.
+narrateur|Une petite.
+narrateur|Une plus grande.
+papa|Tu as vu les traces ?
+enfant-m|Elles sont différentes.
+maman|Oui.
+maman|Les tailles sont différentes.
+narrateur|En ce moment, Aniss ramasse le coquillage.
+narrateur|Le trou laisse passer le ciel.
+narrateur|Sarah arrive, plus grande.
+narrateur|Ses pieds font des traces plus longues.
+enfant-m|Tu viens jouer ?
+enfant-f|Oui.
+maman|On invite.
+maman|On joue ensemble.
+papa|Bravo, Aniss.
+papa|Tu as invité.
+narrateur|Ils posent le coquillage, tout doux.
+narrateur|Le vent pousse encore la serviette.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>oiseau</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1354,7 +1394,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre la cuisine, le jardin, ou la chambre.</t>
+          <t>La mer reste derrière, tout loin. La cuisine, le jardin, ou la chambre ? On invite. On joue ensemble.</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1518,7 +1558,10 @@
       <c r="AV3" s="2" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
+          <t>narrateur|La mer reste derrière, tout loin.
+papa|La cuisine, le jardin, ou la chambre ?
+maman|On invite.
+maman|On joue ensemble.</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1546,7 +1589,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Après la mer, Tom rentre. Il va dans la cuisine. L'eau coule, tout petit bruit. Un copain plus grand lave un coquillage. Tom l'invite. Ils jouent ensemble. Les tailles sont différentes. Maman sourit. On peut jouer ensemble.</t>
+          <t>Après la mer, la cuisine est tiède. L'eau coule, tout petit bruit. Un coquillage attend près de l'évier. Sarah est plus grande. Aniss est plus petit. Les tailles sont différentes. Tu viens ? Oui. On invite. On joue ensemble. Sarah lave le coquillage, tout haut. Aniss tient l'anse, plus bas. Vous jouez ensemble ? Oui, papa. Bravo, Aniss. Tu as invité. Une goutte brille sur le carrelage.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1686,10 +1729,30 @@
       <c r="AV4" s="2" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Après la mer, Tom rentre. Il va dans la cuisine. L'eau coule, tout petit bruit. Un copain plus grand lave un coquillage. Tom l'invite. Ils jouent ensemble. Les tailles sont différentes. Maman sourit. On peut jouer ensemble.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Après la mer, la cuisine est tiède.
+narrateur|L'eau coule, tout petit bruit.
+narrateur|Un coquillage attend près de l'évier.
+narrateur|Sarah est plus grande.
+narrateur|Aniss est plus petit.
+narrateur|Les tailles sont différentes.
+enfant-m|Tu viens ?
+enfant-f|Oui.
+maman|On invite.
+maman|On joue ensemble.
+narrateur|Sarah lave le coquillage, tout haut.
+narrateur|Aniss tient l'anse, plus bas.
+papa|Vous jouez ensemble ?
+enfant-m|Oui, papa.
+papa|Bravo, Aniss.
+papa|Tu as invité.
+narrateur|Une goutte brille sur le carrelage.</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1714,7 +1777,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>On joue ensemble ?</t>
+          <t>Aniss invite Sarah. Ils font quoi ?</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1870,7 +1933,8 @@
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|On joue ensemble ?</t>
+          <t>narrateur|Aniss invite Sarah.
+maman|Ils font quoi ?</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1898,7 +1962,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Oui. On joue ensemble. Tom respire. Maman est là. Les tailles sont différentes. On joue ensemble. On peut jouer ensemble.</t>
+          <t>Oui. On joue ensemble. Aniss souffle un peu. Le coquillage reste mouillé. On joue. Bravo. Tu as invité. Les tailles sont différentes. On peut jouer ensemble. L'eau coule encore, tout fin.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2042,7 +2106,16 @@
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|Oui. On joue ensemble. Tom respire. Maman est là. Les tailles sont différentes. On joue ensemble. On peut jouer ensemble.</t>
+          <t>maman|Oui.
+maman|On joue ensemble.
+narrateur|Aniss souffle un peu.
+narrateur|Le coquillage reste mouillé.
+enfant-m|On joue.
+papa|Bravo.
+papa|Tu as invité.
+maman|Les tailles sont différentes.
+maman|On peut jouer ensemble.
+narrateur|L'eau coule encore, tout fin.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2070,7 +2143,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+          <t>Trois jeux attendent, tout proches. Le ballon rouge, le seau bleu, ou le doudou ? On invite. On joue ensemble.</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -2234,7 +2307,10 @@
       <c r="AV7" s="2" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+          <t>narrateur|Trois jeux attendent, tout proches.
+maman|Le ballon rouge, le seau bleu, ou le doudou ?
+papa|On invite.
+papa|On joue ensemble.</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr"/>
@@ -2262,7 +2338,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Tom pose le ballon rouge près de l'évier. Un copain plus grand le fait rouler, tout doux. Maman montre le geste, lentement. Les tailles sont différentes. On joue ensemble. On peut jouer ensemble.</t>
+          <t>Aniss pose le ballon rouge. Le ballon est un peu sablé. Tu veux jouer ? Oui. Sarah est plus grande. Elle rattrape le ballon, tout haut. Aniss le pousse, plus bas. Les tailles sont différentes. On joue ensemble. Bravo, Aniss. Tu as invité. Le ballon roule, tout doux. Le ballon frôle l'évier, tout doux. On est encore dans la cuisine. On invite. On joue ensemble.</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -2402,10 +2478,29 @@
       <c r="AV8" s="2" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>narrateur|Tom pose le ballon rouge près de l'évier. Un copain plus grand le fait rouler, tout doux. Maman montre le geste, lentement. Les tailles sont différentes. On joue ensemble. On peut jouer ensemble.</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr"/>
+          <t>narrateur|Aniss pose le ballon rouge.
+narrateur|Le ballon est un peu sablé.
+enfant-m|Tu veux jouer ?
+enfant-f|Oui.
+narrateur|Sarah est plus grande.
+narrateur|Elle rattrape le ballon, tout haut.
+narrateur|Aniss le pousse, plus bas.
+maman|Les tailles sont différentes.
+maman|On joue ensemble.
+papa|Bravo, Aniss.
+papa|Tu as invité.
+narrateur|Le ballon roule, tout doux.
+narrateur|Le ballon frôle l'évier, tout doux.
+narrateur|On est encore dans la cuisine.
+maman|On invite.
+maman|On joue ensemble.</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>ballon</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2430,7 +2525,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Trois souvenirs de mer attendent. Le coquillage, le galet, ou le filet ? On joue encore ensemble.</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -2598,7 +2693,9 @@
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|Trois souvenirs de mer attendent.
+papa|Le coquillage, le galet, ou le filet ?
+maman|On joue encore ensemble.</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr"/>
@@ -2626,7 +2723,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Tom a choisi la cuisine. Puis le ballon rouge. Puis Tom. Une pomme brille un peu. J'ai appris. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Tom dit merci à maman.</t>
+          <t>Le coquillage a encore un trou. Aniss le tend à Sarah. Tu regardes ? Oui. Sarah le lève, tout haut. Aniss le voit, plus bas. Les tailles sont différentes. On joue ensemble. Bravo. Tu as invité. Le coquillage sonne contre le ballon. On est encore dans la cuisine. Le ballon rouge est rangé, presque. Vous jouez encore ensemble ? Oui. Oui. Bravo. Les tailles sont différentes. On joue ensemble. Aniss pose le coquillage, tout doux.</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -2766,9 +2863,26 @@
       <c r="AV10" s="2" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>narrateur|Tom a choisi la cuisine. Puis le ballon rouge. Puis Tom. Une pomme brille un peu.
-enfant-m|J'ai appris.
-narrateur|Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Tom dit merci à maman.</t>
+          <t>narrateur|Le coquillage a encore un trou.
+narrateur|Aniss le tend à Sarah.
+enfant-m|Tu regardes ?
+enfant-f|Oui.
+narrateur|Sarah le lève, tout haut.
+narrateur|Aniss le voit, plus bas.
+maman|Les tailles sont différentes.
+maman|On joue ensemble.
+papa|Bravo.
+papa|Tu as invité.
+narrateur|Le coquillage sonne contre le ballon.
+narrateur|On est encore dans la cuisine.
+narrateur|Le ballon rouge est rangé, presque.
+papa|Vous jouez encore ensemble ?
+enfant-m|Oui.
+enfant-f|Oui.
+maman|Bravo.
+maman|Les tailles sont différentes.
+maman|On joue ensemble.
+narrateur|Aniss pose le coquillage, tout doux.</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr"/>
@@ -2796,7 +2910,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a joué ensemble. Oui. Bravo, Aniss. Tu as invité Sarah. Aniss a vécu dans la cuisine. Ils ont joué avec le ballon rouge. Ils ont gardé le coquillage. Le trou du coquillage laisse encore le ciel. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -2936,7 +3050,15 @@
       <c r="AV11" s="2" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|On a joué ensemble.
+enfant-f|Oui.
+maman|Bravo, Aniss.
+papa|Tu as invité Sarah.
+narrateur|Aniss a vécu dans la cuisine.
+narrateur|Ils ont joué avec le ballon rouge.
+narrateur|Ils ont gardé le coquillage.
+narrateur|Le trou du coquillage laisse encore le ciel.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr"/>
@@ -2964,7 +3086,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Tom s'arrête près de Léa. le ballon rouge est rangé. Un ruban reste dans la poche. Tom essuie ses mains. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Tom dit merci à maman.</t>
+          <t>Le galet est lisse, tout gris. Il sent encore la mer. On le pose ensemble ? Oui. Sarah pose le galet, tout doux. On invite. On joue ensemble. Bravo, Aniss. C'est du bon travail. Le galet attend près de l'évier. On est encore dans la cuisine. Le ballon rouge est rangé, presque. Vous jouez encore ensemble ? Oui. Oui. Bravo. Les tailles sont différentes. On joue ensemble. Aniss pose le galet, tout doux.</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -3104,7 +3226,25 @@
       <c r="AV12" s="2" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>narrateur|Tom s'arrête près de Léa. le ballon rouge est rangé. Un ruban reste dans la poche. Tom essuie ses mains. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Tom dit merci à maman.</t>
+          <t>narrateur|Le galet est lisse, tout gris.
+narrateur|Il sent encore la mer.
+enfant-m|On le pose ensemble ?
+enfant-f|Oui.
+narrateur|Sarah pose le galet, tout doux.
+papa|On invite.
+papa|On joue ensemble.
+maman|Bravo, Aniss.
+maman|C'est du bon travail.
+narrateur|Le galet attend près de l'évier.
+narrateur|On est encore dans la cuisine.
+narrateur|Le ballon rouge est rangé, presque.
+papa|Vous jouez encore ensemble ?
+enfant-m|Oui.
+enfant-f|Oui.
+maman|Bravo.
+maman|Les tailles sont différentes.
+maman|On joue ensemble.
+narrateur|Aniss pose le galet, tout doux.</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr"/>
@@ -3132,7 +3272,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a joué ensemble. Oui. Bravo, Aniss. Tu as invité Sarah. Aniss a vécu dans la cuisine. Ils ont joué avec le ballon rouge. Ils ont gardé le galet. Le galet reste lisse, tout calme. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -3272,7 +3412,15 @@
       <c r="AV13" s="2" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|On a joué ensemble.
+enfant-f|Oui.
+maman|Bravo, Aniss.
+papa|Tu as invité Sarah.
+narrateur|Aniss a vécu dans la cuisine.
+narrateur|Ils ont joué avec le ballon rouge.
+narrateur|Ils ont gardé le galet.
+narrateur|Le galet reste lisse, tout calme.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr"/>
@@ -3300,7 +3448,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Tom se souvient de la cuisine. Et de le ballon rouge. Et de Sami. Un crochet tient bien le manteau. Tom range encore un peu, près de maman. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Tom dit merci à maman.</t>
+          <t>Le filet sent le sel, un peu. Sarah le tient, tout haut. Aniss tient un bout, plus bas. On tire doucement ? Oui. Les tailles sont différentes. On peut jouer ensemble. Bravo. Vous jouez ensemble. Le filet sèche près du ballon rouge. On est encore dans la cuisine. Le ballon rouge est rangé, presque. Vous jouez encore ensemble ? Oui. Oui. Bravo. Les tailles sont différentes. On joue ensemble. Aniss pose le filet, tout doux.</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -3440,7 +3588,25 @@
       <c r="AV14" s="2" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>narrateur|Tom se souvient de la cuisine. Et de le ballon rouge. Et de Sami. Un crochet tient bien le manteau. Tom range encore un peu, près de maman. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Tom dit merci à maman.</t>
+          <t>narrateur|Le filet sent le sel, un peu.
+narrateur|Sarah le tient, tout haut.
+narrateur|Aniss tient un bout, plus bas.
+enfant-m|On tire doucement ?
+enfant-f|Oui.
+maman|Les tailles sont différentes.
+maman|On peut jouer ensemble.
+papa|Bravo.
+papa|Vous jouez ensemble.
+narrateur|Le filet sèche près du ballon rouge.
+narrateur|On est encore dans la cuisine.
+narrateur|Le ballon rouge est rangé, presque.
+papa|Vous jouez encore ensemble ?
+enfant-m|Oui.
+enfant-f|Oui.
+maman|Bravo.
+maman|Les tailles sont différentes.
+maman|On joue ensemble.
+narrateur|Aniss pose le filet, tout doux.</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr"/>
@@ -3468,7 +3634,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a joué ensemble. Oui. Bravo, Aniss. Tu as invité Sarah. Aniss a vécu dans la cuisine. Ils ont joué avec le ballon rouge. Ils ont gardé le filet. Le filet sent encore le sel, tout loin. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -3608,7 +3774,15 @@
       <c r="AV15" s="2" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|On a joué ensemble.
+enfant-f|Oui.
+maman|Bravo, Aniss.
+papa|Tu as invité Sarah.
+narrateur|Aniss a vécu dans la cuisine.
+narrateur|Ils ont joué avec le ballon rouge.
+narrateur|Ils ont gardé le filet.
+narrateur|Le filet sent encore le sel, tout loin.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr"/>
@@ -3636,7 +3810,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Tom remplit le seau bleu. Un copain plus petit tient l'anse avec lui. Je suis là. Les tailles sont différentes. On joue ensemble. On peut jouer ensemble.</t>
+          <t>Aniss prend le seau bleu. L'anse est un peu rêche. On le tient ensemble ? Oui. Sarah tient l'anse, tout haut. Aniss tient le bord, plus bas. Les tailles sont différentes. On peut jouer ensemble. Bravo. Vous jouez ensemble. Un peu d'eau tremble, dans le seau. Le seau pose sous le robinet. On est encore dans la cuisine. On invite. On joue ensemble.</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -3776,12 +3950,28 @@
       <c r="AV16" s="2" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>narrateur|Tom remplit le seau bleu. Un copain plus petit tient l'anse avec lui.
-maman|Je suis là.
-narrateur|Les tailles sont différentes. On joue ensemble. On peut jouer ensemble.</t>
-        </is>
-      </c>
-      <c r="AX16" t="inlineStr"/>
+          <t>narrateur|Aniss prend le seau bleu.
+narrateur|L'anse est un peu rêche.
+enfant-m|On le tient ensemble ?
+enfant-f|Oui.
+narrateur|Sarah tient l'anse, tout haut.
+narrateur|Aniss tient le bord, plus bas.
+papa|Les tailles sont différentes.
+papa|On peut jouer ensemble.
+maman|Bravo.
+maman|Vous jouez ensemble.
+narrateur|Un peu d'eau tremble, dans le seau.
+narrateur|Le seau pose sous le robinet.
+narrateur|On est encore dans la cuisine.
+maman|On invite.
+maman|On joue ensemble.</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3806,7 +3996,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Trois souvenirs de mer attendent. Le coquillage, le galet, ou le filet ? On joue encore ensemble.</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -3974,7 +4164,9 @@
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|Trois souvenirs de mer attendent.
+papa|Le coquillage, le galet, ou le filet ?
+maman|On joue encore ensemble.</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr"/>
@@ -4002,7 +4194,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Avec Tom. Après le seau bleu. Près de la cuisine. Tom s'arrête. L'eau coule, tout petit bruit. Tom répète tout bas le geste. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Tom dit merci à maman.</t>
+          <t>Le coquillage a encore un trou. Aniss le tend à Sarah. Tu regardes ? Oui. Sarah le lève, tout haut. Aniss le voit, plus bas. Les tailles sont différentes. On joue ensemble. Bravo. Tu as invité. Le coquillage trempe dans le seau. On est encore dans la cuisine. Le seau bleu est rangé, presque. Vous jouez encore ensemble ? Oui. Oui. Bravo. Les tailles sont différentes. On joue ensemble. Aniss pose le coquillage, tout doux.</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -4142,7 +4334,26 @@
       <c r="AV18" s="2" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>narrateur|Avec Tom. Après le seau bleu. Près de la cuisine. Tom s'arrête. L'eau coule, tout petit bruit. Tom répète tout bas le geste. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Tom dit merci à maman.</t>
+          <t>narrateur|Le coquillage a encore un trou.
+narrateur|Aniss le tend à Sarah.
+enfant-m|Tu regardes ?
+enfant-f|Oui.
+narrateur|Sarah le lève, tout haut.
+narrateur|Aniss le voit, plus bas.
+maman|Les tailles sont différentes.
+maman|On joue ensemble.
+papa|Bravo.
+papa|Tu as invité.
+narrateur|Le coquillage trempe dans le seau.
+narrateur|On est encore dans la cuisine.
+narrateur|Le seau bleu est rangé, presque.
+papa|Vous jouez encore ensemble ?
+enfant-m|Oui.
+enfant-f|Oui.
+maman|Bravo.
+maman|Les tailles sont différentes.
+maman|On joue ensemble.
+narrateur|Aniss pose le coquillage, tout doux.</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr"/>
@@ -4170,7 +4381,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a joué ensemble. Oui. Bravo, Aniss. Tu as invité Sarah. Aniss a vécu dans la cuisine. Ils ont joué avec le seau bleu. Ils ont gardé le coquillage. Le trou du coquillage laisse encore le ciel. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -4310,7 +4521,15 @@
       <c r="AV19" s="2" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|On a joué ensemble.
+enfant-f|Oui.
+maman|Bravo, Aniss.
+papa|Tu as invité Sarah.
+narrateur|Aniss a vécu dans la cuisine.
+narrateur|Ils ont joué avec le seau bleu.
+narrateur|Ils ont gardé le coquillage.
+narrateur|Le trou du coquillage laisse encore le ciel.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr"/>
@@ -4338,7 +4557,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Tom range le seau bleu. Léa reste près de la cuisine. Ça sent le pain chaud. Tom montre Léa à maman. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Tom dit merci à maman.</t>
+          <t>Le galet est lisse, tout gris. Il sent encore la mer. On le pose ensemble ? Oui. Sarah pose le galet, tout doux. On invite. On joue ensemble. Bravo, Aniss. C'est du bon travail. Le galet pèse au fond du seau. On est encore dans la cuisine. Le seau bleu est rangé, presque. Vous jouez encore ensemble ? Oui. Oui. Bravo. Les tailles sont différentes. On joue ensemble. Aniss pose le galet, tout doux.</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -4478,7 +4697,25 @@
       <c r="AV20" s="2" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>narrateur|Tom range le seau bleu. Léa reste près de la cuisine. Ça sent le pain chaud. Tom montre Léa à maman. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Tom dit merci à maman.</t>
+          <t>narrateur|Le galet est lisse, tout gris.
+narrateur|Il sent encore la mer.
+enfant-m|On le pose ensemble ?
+enfant-f|Oui.
+narrateur|Sarah pose le galet, tout doux.
+papa|On invite.
+papa|On joue ensemble.
+maman|Bravo, Aniss.
+maman|C'est du bon travail.
+narrateur|Le galet pèse au fond du seau.
+narrateur|On est encore dans la cuisine.
+narrateur|Le seau bleu est rangé, presque.
+papa|Vous jouez encore ensemble ?
+enfant-m|Oui.
+enfant-f|Oui.
+maman|Bravo.
+maman|Les tailles sont différentes.
+maman|On joue ensemble.
+narrateur|Aniss pose le galet, tout doux.</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr"/>
@@ -4506,7 +4743,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a joué ensemble. Oui. Bravo, Aniss. Tu as invité Sarah. Aniss a vécu dans la cuisine. Ils ont joué avec le seau bleu. Ils ont gardé le galet. Le galet reste lisse, tout calme. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -4646,7 +4883,15 @@
       <c r="AV21" s="2" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|On a joué ensemble.
+enfant-f|Oui.
+maman|Bravo, Aniss.
+papa|Tu as invité Sarah.
+narrateur|Aniss a vécu dans la cuisine.
+narrateur|Ils ont joué avec le seau bleu.
+narrateur|Ils ont gardé le galet.
+narrateur|Le galet reste lisse, tout calme.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr"/>
@@ -4674,7 +4919,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Sami est là. le seau bleu aussi. la cuisine reste dans le souvenir. Un chat miaule une fois. Tom pose sa tête un moment. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Tom dit merci à maman.</t>
+          <t>Le filet sent le sel, un peu. Sarah le tient, tout haut. Aniss tient un bout, plus bas. On tire doucement ? Oui. Les tailles sont différentes. On peut jouer ensemble. Bravo. Vous jouez ensemble. Le filet goutte au-dessus du seau. On est encore dans la cuisine. Le seau bleu est rangé, presque. Vous jouez encore ensemble ? Oui. Oui. Bravo. Les tailles sont différentes. On joue ensemble. Aniss pose le filet, tout doux.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -4814,7 +5059,25 @@
       <c r="AV22" s="2" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>narrateur|Sami est là. le seau bleu aussi. la cuisine reste dans le souvenir. Un chat miaule une fois. Tom pose sa tête un moment. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Tom dit merci à maman.</t>
+          <t>narrateur|Le filet sent le sel, un peu.
+narrateur|Sarah le tient, tout haut.
+narrateur|Aniss tient un bout, plus bas.
+enfant-m|On tire doucement ?
+enfant-f|Oui.
+maman|Les tailles sont différentes.
+maman|On peut jouer ensemble.
+papa|Bravo.
+papa|Vous jouez ensemble.
+narrateur|Le filet goutte au-dessus du seau.
+narrateur|On est encore dans la cuisine.
+narrateur|Le seau bleu est rangé, presque.
+papa|Vous jouez encore ensemble ?
+enfant-m|Oui.
+enfant-f|Oui.
+maman|Bravo.
+maman|Les tailles sont différentes.
+maman|On joue ensemble.
+narrateur|Aniss pose le filet, tout doux.</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr"/>
@@ -4842,7 +5105,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a joué ensemble. Oui. Bravo, Aniss. Tu as invité Sarah. Aniss a vécu dans la cuisine. Ils ont joué avec le seau bleu. Ils ont gardé le filet. Le filet sent encore le sel, tout loin. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -4982,7 +5245,15 @@
       <c r="AV23" s="2" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|On a joué ensemble.
+enfant-f|Oui.
+maman|Bravo, Aniss.
+papa|Tu as invité Sarah.
+narrateur|Aniss a vécu dans la cuisine.
+narrateur|Ils ont joué avec le seau bleu.
+narrateur|Ils ont gardé le filet.
+narrateur|Le filet sent encore le sel, tout loin.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr"/>
@@ -5010,7 +5281,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Tom pose le doudou sur une chaise sèche. Un copain d'une autre taille le caresse. Maman reste tout près. Les tailles sont différentes. On joue ensemble. On peut jouer ensemble.</t>
+          <t>Aniss pose le doudou. Le tissu est encore sablé. Tu le caresses ? Oui. Sarah est plus grande. Sa main couvre presque le doudou. La main d'Aniss est plus petite. On invite. On joue ensemble. Bravo, Aniss. Tu as invité Sarah. Le doudou a une oreille froissée. Le doudou s'assoit sur une chaise sèche. On est encore dans la cuisine. On invite. On joue ensemble.</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -5150,7 +5421,22 @@
       <c r="AV24" s="2" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>narrateur|Tom pose le doudou sur une chaise sèche. Un copain d'une autre taille le caresse. Maman reste tout près. Les tailles sont différentes. On joue ensemble. On peut jouer ensemble.</t>
+          <t>narrateur|Aniss pose le doudou.
+narrateur|Le tissu est encore sablé.
+enfant-m|Tu le caresses ?
+enfant-f|Oui.
+narrateur|Sarah est plus grande.
+narrateur|Sa main couvre presque le doudou.
+narrateur|La main d'Aniss est plus petite.
+maman|On invite.
+maman|On joue ensemble.
+papa|Bravo, Aniss.
+papa|Tu as invité Sarah.
+narrateur|Le doudou a une oreille froissée.
+narrateur|Le doudou s'assoit sur une chaise sèche.
+narrateur|On est encore dans la cuisine.
+maman|On invite.
+maman|On joue ensemble.</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr"/>
@@ -5178,7 +5464,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Trois souvenirs de mer attendent. Le coquillage, le galet, ou le filet ? On joue encore ensemble.</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -5346,7 +5632,9 @@
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|Trois souvenirs de mer attendent.
+papa|Le coquillage, le galet, ou le filet ?
+maman|On joue encore ensemble.</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr"/>
@@ -5374,7 +5662,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Tom rejoint Tom. le doudou est rangé. la cuisine est fini. Il y a des miettes sur la table. Tom pose le doudou à sa place. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Tom dit merci à maman.</t>
+          <t>Le coquillage a encore un trou. Aniss le tend à Sarah. Tu regardes ? Oui. Sarah le lève, tout haut. Aniss le voit, plus bas. Les tailles sont différentes. On joue ensemble. Bravo. Tu as invité. Le coquillage dort près du doudou. On est encore dans la cuisine. Le doudou est rangé, presque. Vous jouez encore ensemble ? Oui. Oui. Bravo. Les tailles sont différentes. On joue ensemble. Aniss pose le coquillage, tout doux.</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -5514,7 +5802,26 @@
       <c r="AV26" s="2" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>narrateur|Tom rejoint Tom. le doudou est rangé. la cuisine est fini. Il y a des miettes sur la table. Tom pose le doudou à sa place. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Tom dit merci à maman.</t>
+          <t>narrateur|Le coquillage a encore un trou.
+narrateur|Aniss le tend à Sarah.
+enfant-m|Tu regardes ?
+enfant-f|Oui.
+narrateur|Sarah le lève, tout haut.
+narrateur|Aniss le voit, plus bas.
+maman|Les tailles sont différentes.
+maman|On joue ensemble.
+papa|Bravo.
+papa|Tu as invité.
+narrateur|Le coquillage dort près du doudou.
+narrateur|On est encore dans la cuisine.
+narrateur|Le doudou est rangé, presque.
+papa|Vous jouez encore ensemble ?
+enfant-m|Oui.
+enfant-f|Oui.
+maman|Bravo.
+maman|Les tailles sont différentes.
+maman|On joue ensemble.
+narrateur|Aniss pose le coquillage, tout doux.</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr"/>
@@ -5542,7 +5849,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a joué ensemble. Oui. Bravo, Aniss. Tu as invité Sarah. Aniss a vécu dans la cuisine. Ils ont joué avec le doudou. Ils ont gardé le coquillage. Le trou du coquillage laisse encore le ciel. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -5682,7 +5989,15 @@
       <c r="AV27" s="2" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|On a joué ensemble.
+enfant-f|Oui.
+maman|Bravo, Aniss.
+papa|Tu as invité Sarah.
+narrateur|Aniss a vécu dans la cuisine.
+narrateur|Ils ont joué avec le doudou.
+narrateur|Ils ont gardé le coquillage.
+narrateur|Le trou du coquillage laisse encore le ciel.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr"/>
@@ -5710,7 +6025,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Près de Léa. Tom pose le doudou. la cuisine est derrière. La lumière est claire. Tom caresse le doudou. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Tom dit merci à maman.</t>
+          <t>Le galet est lisse, tout gris. Il sent encore la mer. On le pose ensemble ? Oui. Sarah pose le galet, tout doux. On invite. On joue ensemble. Bravo, Aniss. C'est du bon travail. Le galet chauffe contre le doudou. On est encore dans la cuisine. Le doudou est rangé, presque. Vous jouez encore ensemble ? Oui. Oui. Bravo. Les tailles sont différentes. On joue ensemble. Aniss pose le galet, tout doux.</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -5850,7 +6165,25 @@
       <c r="AV28" s="2" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>narrateur|Près de Léa. Tom pose le doudou. la cuisine est derrière. La lumière est claire. Tom caresse le doudou. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Tom dit merci à maman.</t>
+          <t>narrateur|Le galet est lisse, tout gris.
+narrateur|Il sent encore la mer.
+enfant-m|On le pose ensemble ?
+enfant-f|Oui.
+narrateur|Sarah pose le galet, tout doux.
+papa|On invite.
+papa|On joue ensemble.
+maman|Bravo, Aniss.
+maman|C'est du bon travail.
+narrateur|Le galet chauffe contre le doudou.
+narrateur|On est encore dans la cuisine.
+narrateur|Le doudou est rangé, presque.
+papa|Vous jouez encore ensemble ?
+enfant-m|Oui.
+enfant-f|Oui.
+maman|Bravo.
+maman|Les tailles sont différentes.
+maman|On joue ensemble.
+narrateur|Aniss pose le galet, tout doux.</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr"/>
@@ -5878,7 +6211,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a joué ensemble. Oui. Bravo, Aniss. Tu as invité Sarah. Aniss a vécu dans la cuisine. Ils ont joué avec le doudou. Ils ont gardé le galet. Le galet reste lisse, tout calme. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -6018,7 +6351,15 @@
       <c r="AV29" s="2" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|On a joué ensemble.
+enfant-f|Oui.
+maman|Bravo, Aniss.
+papa|Tu as invité Sarah.
+narrateur|Aniss a vécu dans la cuisine.
+narrateur|Ils ont joué avec le doudou.
+narrateur|Ils ont gardé le galet.
+narrateur|Le galet reste lisse, tout calme.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr"/>
@@ -6046,7 +6387,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Tom montre Sami. Maman a vu la cuisine. Et le doudou. Un vélo passe au loin. Tom range la cuisine dans sa tête, comme un souvenir. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Tom dit merci à maman.</t>
+          <t>Le filet sent le sel, un peu. Sarah le tient, tout haut. Aniss tient un bout, plus bas. On tire doucement ? Oui. Les tailles sont différentes. On peut jouer ensemble. Bravo. Vous jouez ensemble. Le filet couvre un peu le doudou. On est encore dans la cuisine. Le doudou est rangé, presque. Vous jouez encore ensemble ? Oui. Oui. Bravo. Les tailles sont différentes. On joue ensemble. Aniss pose le filet, tout doux.</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -6186,7 +6527,25 @@
       <c r="AV30" s="2" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>narrateur|Tom montre Sami. Maman a vu la cuisine. Et le doudou. Un vélo passe au loin. Tom range la cuisine dans sa tête, comme un souvenir. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Tom dit merci à maman.</t>
+          <t>narrateur|Le filet sent le sel, un peu.
+narrateur|Sarah le tient, tout haut.
+narrateur|Aniss tient un bout, plus bas.
+enfant-m|On tire doucement ?
+enfant-f|Oui.
+maman|Les tailles sont différentes.
+maman|On peut jouer ensemble.
+papa|Bravo.
+papa|Vous jouez ensemble.
+narrateur|Le filet couvre un peu le doudou.
+narrateur|On est encore dans la cuisine.
+narrateur|Le doudou est rangé, presque.
+papa|Vous jouez encore ensemble ?
+enfant-m|Oui.
+enfant-f|Oui.
+maman|Bravo.
+maman|Les tailles sont différentes.
+maman|On joue ensemble.
+narrateur|Aniss pose le filet, tout doux.</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr"/>
@@ -6214,7 +6573,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a joué ensemble. Oui. Bravo, Aniss. Tu as invité Sarah. Aniss a vécu dans la cuisine. Ils ont joué avec le doudou. Ils ont gardé le filet. Le filet sent encore le sel, tout loin. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -6354,7 +6713,15 @@
       <c r="AV31" s="2" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|On a joué ensemble.
+enfant-f|Oui.
+maman|Bravo, Aniss.
+papa|Tu as invité Sarah.
+narrateur|Aniss a vécu dans la cuisine.
+narrateur|Ils ont joué avec le doudou.
+narrateur|Ils ont gardé le filet.
+narrateur|Le filet sent encore le sel, tout loin.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr"/>
@@ -6382,7 +6749,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Après la mer, Tom va dans le jardin. L'herbe est tiède. Un copain plus petit tient un arrosoir. Tom l'invite. Ils versent l'eau, tout doux. Ils jouent ensemble. Les tailles sont différentes. Maman est là. On peut jouer ensemble.</t>
+          <t>Après la mer, l'herbe est tiède. Un linge sèche, tout blanc. Sarah tient un arrosoir, plus haut. Aniss tient une pelle, plus petite. Les tailles sont différentes. On verse l'eau ? Oui. On invite. On joue ensemble. Ils versent, tout doux. L'eau fait un petit cercle. Bravo. Vous jouez ensemble. Sarah est grande. Et toi, plus petit. On peut jouer ensemble. Une feuille colle à la chaussette.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6522,10 +6889,30 @@
       <c r="AV32" s="2" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>narrateur|Après la mer, Tom va dans le jardin. L'herbe est tiède. Un copain plus petit tient un arrosoir. Tom l'invite. Ils versent l'eau, tout doux. Ils jouent ensemble. Les tailles sont différentes. Maman est là. On peut jouer ensemble.</t>
-        </is>
-      </c>
-      <c r="AX32" t="inlineStr"/>
+          <t>narrateur|Après la mer, l'herbe est tiède.
+narrateur|Un linge sèche, tout blanc.
+narrateur|Sarah tient un arrosoir, plus haut.
+narrateur|Aniss tient une pelle, plus petite.
+narrateur|Les tailles sont différentes.
+enfant-m|On verse l'eau ?
+enfant-f|Oui.
+maman|On invite.
+maman|On joue ensemble.
+narrateur|Ils versent, tout doux.
+narrateur|L'eau fait un petit cercle.
+papa|Bravo.
+papa|Vous jouez ensemble.
+enfant-m|Sarah est grande.
+maman|Et toi, plus petit.
+maman|On peut jouer ensemble.
+narrateur|Une feuille colle à la chaussette.</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>oiseau</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6710,7 +7097,8 @@
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>narrateur|Les tailles sont différentes. On fait quoi ?</t>
+          <t>narrateur|Les tailles sont différentes.
+papa|On fait quoi ?</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr"/>
@@ -6738,7 +7126,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Oui. On joue ensemble. Tom retient le geste. Maman sourit. Les tailles sont différentes. On joue ensemble. On peut jouer ensemble.</t>
+          <t>Oui. On joue ensemble. Aniss tient encore la pelle. On invite. Bravo, Aniss. C'est du bon travail. Sarah verse une dernière goutte. Les tailles sont différentes. L'herbe brille, tout calme.</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -6882,7 +7270,15 @@
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>narrateur|Oui. On joue ensemble. Tom retient le geste. Maman sourit. Les tailles sont différentes. On joue ensemble. On peut jouer ensemble.</t>
+          <t>papa|Oui.
+papa|On joue ensemble.
+narrateur|Aniss tient encore la pelle.
+enfant-m|On invite.
+maman|Bravo, Aniss.
+maman|C'est du bon travail.
+narrateur|Sarah verse une dernière goutte.
+maman|Les tailles sont différentes.
+narrateur|L'herbe brille, tout calme.</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr"/>
@@ -6910,7 +7306,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+          <t>Trois jeux attendent, tout proches. Le ballon rouge, le seau bleu, ou le doudou ? On invite. On joue ensemble.</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -7074,7 +7470,10 @@
       <c r="AV35" s="2" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+          <t>narrateur|Trois jeux attendent, tout proches.
+maman|Le ballon rouge, le seau bleu, ou le doudou ?
+papa|On invite.
+papa|On joue ensemble.</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr"/>
@@ -7102,7 +7501,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Tom fait rouler le ballon rouge dans l'herbe. Un copain plus grand le rattrape. Je suis là. Les tailles sont différentes. On joue ensemble. On peut jouer ensemble.</t>
+          <t>Aniss pose le ballon rouge. Le ballon est un peu sablé. Tu veux jouer ? Oui. Sarah est plus grande. Elle rattrape le ballon, tout haut. Aniss le pousse, plus bas. Les tailles sont différentes. On joue ensemble. Bravo, Aniss. Tu as invité. Le ballon roule, tout doux. Le ballon roule dans l'herbe tiède. On est encore dans le jardin. On invite. On joue ensemble.</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -7242,12 +7641,29 @@
       <c r="AV36" s="2" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>narrateur|Tom fait rouler le ballon rouge dans l'herbe. Un copain plus grand le rattrape.
-maman|Je suis là.
-narrateur|Les tailles sont différentes. On joue ensemble. On peut jouer ensemble.</t>
-        </is>
-      </c>
-      <c r="AX36" t="inlineStr"/>
+          <t>narrateur|Aniss pose le ballon rouge.
+narrateur|Le ballon est un peu sablé.
+enfant-m|Tu veux jouer ?
+enfant-f|Oui.
+narrateur|Sarah est plus grande.
+narrateur|Elle rattrape le ballon, tout haut.
+narrateur|Aniss le pousse, plus bas.
+maman|Les tailles sont différentes.
+maman|On joue ensemble.
+papa|Bravo, Aniss.
+papa|Tu as invité.
+narrateur|Le ballon roule, tout doux.
+narrateur|Le ballon roule dans l'herbe tiède.
+narrateur|On est encore dans le jardin.
+maman|On invite.
+maman|On joue ensemble.</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>ballon</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7272,7 +7688,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Trois souvenirs de mer attendent. Le coquillage, le galet, ou le filet ? On joue encore ensemble.</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -7440,7 +7856,9 @@
       </c>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|Trois souvenirs de mer attendent.
+papa|Le coquillage, le galet, ou le filet ?
+maman|On joue encore ensemble.</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr"/>
@@ -7468,7 +7886,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Tom a choisi le jardin. Puis le ballon rouge. Puis Tom. Un linge sèche à l'air. Tom tend Tom à papa. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Tom dit merci à maman.</t>
+          <t>Le coquillage a encore un trou. Aniss le tend à Sarah. Tu regardes ? Oui. Sarah le lève, tout haut. Aniss le voit, plus bas. Les tailles sont différentes. On joue ensemble. Bravo. Tu as invité. Le coquillage brille dans l'herbe. On est encore dans le jardin. Le ballon rouge est rangé, presque. Vous jouez encore ensemble ? Oui. Oui. Bravo. Les tailles sont différentes. On joue ensemble. Aniss pose le coquillage, tout doux.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -7608,7 +8026,26 @@
       <c r="AV38" s="2" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>narrateur|Tom a choisi le jardin. Puis le ballon rouge. Puis Tom. Un linge sèche à l'air. Tom tend Tom à papa. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Tom dit merci à maman.</t>
+          <t>narrateur|Le coquillage a encore un trou.
+narrateur|Aniss le tend à Sarah.
+enfant-m|Tu regardes ?
+enfant-f|Oui.
+narrateur|Sarah le lève, tout haut.
+narrateur|Aniss le voit, plus bas.
+maman|Les tailles sont différentes.
+maman|On joue ensemble.
+papa|Bravo.
+papa|Tu as invité.
+narrateur|Le coquillage brille dans l'herbe.
+narrateur|On est encore dans le jardin.
+narrateur|Le ballon rouge est rangé, presque.
+papa|Vous jouez encore ensemble ?
+enfant-m|Oui.
+enfant-f|Oui.
+maman|Bravo.
+maman|Les tailles sont différentes.
+maman|On joue ensemble.
+narrateur|Aniss pose le coquillage, tout doux.</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr"/>
@@ -7636,7 +8073,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a joué ensemble. Oui. Bravo, Aniss. Tu as invité Sarah. Aniss a vécu dans le jardin. Ils ont joué avec le ballon rouge. Ils ont gardé le coquillage. Le trou du coquillage laisse encore le ciel. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -7776,7 +8213,15 @@
       <c r="AV39" s="2" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|On a joué ensemble.
+enfant-f|Oui.
+maman|Bravo, Aniss.
+papa|Tu as invité Sarah.
+narrateur|Aniss a vécu dans le jardin.
+narrateur|Ils ont joué avec le ballon rouge.
+narrateur|Ils ont gardé le coquillage.
+narrateur|Le trou du coquillage laisse encore le ciel.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr"/>
@@ -7804,7 +8249,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Tom s'arrête près de Léa. le ballon rouge est rangé. Le vent est doux. Papa n'est pas loin. Tom les rejoint. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Tom dit merci à maman.</t>
+          <t>Le galet est lisse, tout gris. Il sent encore la mer. On le pose ensemble ? Oui. Sarah pose le galet, tout doux. On invite. On joue ensemble. Bravo, Aniss. C'est du bon travail. Le galet arrête le ballon, tout doux. On est encore dans le jardin. Le ballon rouge est rangé, presque. Vous jouez encore ensemble ? Oui. Oui. Bravo. Les tailles sont différentes. On joue ensemble. Aniss pose le galet, tout doux.</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -7944,7 +8389,25 @@
       <c r="AV40" s="2" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>narrateur|Tom s'arrête près de Léa. le ballon rouge est rangé. Le vent est doux. Papa n'est pas loin. Tom les rejoint. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Tom dit merci à maman.</t>
+          <t>narrateur|Le galet est lisse, tout gris.
+narrateur|Il sent encore la mer.
+enfant-m|On le pose ensemble ?
+enfant-f|Oui.
+narrateur|Sarah pose le galet, tout doux.
+papa|On invite.
+papa|On joue ensemble.
+maman|Bravo, Aniss.
+maman|C'est du bon travail.
+narrateur|Le galet arrête le ballon, tout doux.
+narrateur|On est encore dans le jardin.
+narrateur|Le ballon rouge est rangé, presque.
+papa|Vous jouez encore ensemble ?
+enfant-m|Oui.
+enfant-f|Oui.
+maman|Bravo.
+maman|Les tailles sont différentes.
+maman|On joue ensemble.
+narrateur|Aniss pose le galet, tout doux.</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr"/>
@@ -7972,7 +8435,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a joué ensemble. Oui. Bravo, Aniss. Tu as invité Sarah. Aniss a vécu dans le jardin. Ils ont joué avec le ballon rouge. Ils ont gardé le galet. Le galet reste lisse, tout calme. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -8112,7 +8575,15 @@
       <c r="AV41" s="2" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|On a joué ensemble.
+enfant-f|Oui.
+maman|Bravo, Aniss.
+papa|Tu as invité Sarah.
+narrateur|Aniss a vécu dans le jardin.
+narrateur|Ils ont joué avec le ballon rouge.
+narrateur|Ils ont gardé le galet.
+narrateur|Le galet reste lisse, tout calme.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr"/>
@@ -8140,7 +8611,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Tom se souvient de le jardin. Et de le ballon rouge. Et de Sami. On attend son tour. Tom marche près de maman. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Tom dit merci à maman.</t>
+          <t>Le filet sent le sel, un peu. Sarah le tient, tout haut. Aniss tient un bout, plus bas. On tire doucement ? Oui. Les tailles sont différentes. On peut jouer ensemble. Bravo. Vous jouez ensemble. Le filet sèche au vent, près du ballon. On est encore dans le jardin. Le ballon rouge est rangé, presque. Vous jouez encore ensemble ? Oui. Oui. Bravo. Les tailles sont différentes. On joue ensemble. Aniss pose le filet, tout doux.</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -8280,7 +8751,25 @@
       <c r="AV42" s="2" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>narrateur|Tom se souvient de le jardin. Et de le ballon rouge. Et de Sami. On attend son tour. Tom marche près de maman. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Tom dit merci à maman.</t>
+          <t>narrateur|Le filet sent le sel, un peu.
+narrateur|Sarah le tient, tout haut.
+narrateur|Aniss tient un bout, plus bas.
+enfant-m|On tire doucement ?
+enfant-f|Oui.
+maman|Les tailles sont différentes.
+maman|On peut jouer ensemble.
+papa|Bravo.
+papa|Vous jouez ensemble.
+narrateur|Le filet sèche au vent, près du ballon.
+narrateur|On est encore dans le jardin.
+narrateur|Le ballon rouge est rangé, presque.
+papa|Vous jouez encore ensemble ?
+enfant-m|Oui.
+enfant-f|Oui.
+maman|Bravo.
+maman|Les tailles sont différentes.
+maman|On joue ensemble.
+narrateur|Aniss pose le filet, tout doux.</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr"/>
@@ -8308,7 +8797,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a joué ensemble. Oui. Bravo, Aniss. Tu as invité Sarah. Aniss a vécu dans le jardin. Ils ont joué avec le ballon rouge. Ils ont gardé le filet. Le filet sent encore le sel, tout loin. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -8448,7 +8937,15 @@
       <c r="AV43" s="2" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|On a joué ensemble.
+enfant-f|Oui.
+maman|Bravo, Aniss.
+papa|Tu as invité Sarah.
+narrateur|Aniss a vécu dans le jardin.
+narrateur|Ils ont joué avec le ballon rouge.
+narrateur|Ils ont gardé le filet.
+narrateur|Le filet sent encore le sel, tout loin.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr"/>
@@ -8476,7 +8973,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Tom pose le seau bleu sous le robinet du jardin. Un copain plus petit rit un peu. Maman reste tout près. Les tailles sont différentes. On joue ensemble. On peut jouer ensemble.</t>
+          <t>Aniss prend le seau bleu. L'anse est un peu rêche. On le tient ensemble ? Oui. Sarah tient l'anse, tout haut. Aniss tient le bord, plus bas. Les tailles sont différentes. On peut jouer ensemble. Bravo. Vous jouez ensemble. Un peu d'eau tremble, dans le seau. Le seau attend sous le robinet du jardin. On est encore dans le jardin. On invite. On joue ensemble.</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -8616,10 +9113,28 @@
       <c r="AV44" s="2" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>narrateur|Tom pose le seau bleu sous le robinet du jardin. Un copain plus petit rit un peu. Maman reste tout près. Les tailles sont différentes. On joue ensemble. On peut jouer ensemble.</t>
-        </is>
-      </c>
-      <c r="AX44" t="inlineStr"/>
+          <t>narrateur|Aniss prend le seau bleu.
+narrateur|L'anse est un peu rêche.
+enfant-m|On le tient ensemble ?
+enfant-f|Oui.
+narrateur|Sarah tient l'anse, tout haut.
+narrateur|Aniss tient le bord, plus bas.
+papa|Les tailles sont différentes.
+papa|On peut jouer ensemble.
+maman|Bravo.
+maman|Vous jouez ensemble.
+narrateur|Un peu d'eau tremble, dans le seau.
+narrateur|Le seau attend sous le robinet du jardin.
+narrateur|On est encore dans le jardin.
+maman|On invite.
+maman|On joue ensemble.</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8644,7 +9159,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Trois souvenirs de mer attendent. Le coquillage, le galet, ou le filet ? On joue encore ensemble.</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -8812,7 +9327,9 @@
       </c>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|Trois souvenirs de mer attendent.
+papa|Le coquillage, le galet, ou le filet ?
+maman|On joue encore ensemble.</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr"/>
@@ -8840,7 +9357,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Avec Tom. Après le seau bleu. Près de le jardin. Tom s'arrête. Un panier est posé sur le banc. Tom range la tasse. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Tom dit merci à maman.</t>
+          <t>Le coquillage a encore un trou. Aniss le tend à Sarah. Tu regardes ? Oui. Sarah le lève, tout haut. Aniss le voit, plus bas. Les tailles sont différentes. On joue ensemble. Bravo. Tu as invité. Le coquillage flotte dans le seau. On est encore dans le jardin. Le seau bleu est rangé, presque. Vous jouez encore ensemble ? Oui. Oui. Bravo. Les tailles sont différentes. On joue ensemble. Aniss pose le coquillage, tout doux.</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -8980,7 +9497,26 @@
       <c r="AV46" s="2" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>narrateur|Avec Tom. Après le seau bleu. Près de le jardin. Tom s'arrête. Un panier est posé sur le banc. Tom range la tasse. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Tom dit merci à maman.</t>
+          <t>narrateur|Le coquillage a encore un trou.
+narrateur|Aniss le tend à Sarah.
+enfant-m|Tu regardes ?
+enfant-f|Oui.
+narrateur|Sarah le lève, tout haut.
+narrateur|Aniss le voit, plus bas.
+maman|Les tailles sont différentes.
+maman|On joue ensemble.
+papa|Bravo.
+papa|Tu as invité.
+narrateur|Le coquillage flotte dans le seau.
+narrateur|On est encore dans le jardin.
+narrateur|Le seau bleu est rangé, presque.
+papa|Vous jouez encore ensemble ?
+enfant-m|Oui.
+enfant-f|Oui.
+maman|Bravo.
+maman|Les tailles sont différentes.
+maman|On joue ensemble.
+narrateur|Aniss pose le coquillage, tout doux.</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr"/>
@@ -9008,7 +9544,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a joué ensemble. Oui. Bravo, Aniss. Tu as invité Sarah. Aniss a vécu dans le jardin. Ils ont joué avec le seau bleu. Ils ont gardé le coquillage. Le trou du coquillage laisse encore le ciel. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -9148,7 +9684,15 @@
       <c r="AV47" s="2" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|On a joué ensemble.
+enfant-f|Oui.
+maman|Bravo, Aniss.
+papa|Tu as invité Sarah.
+narrateur|Aniss a vécu dans le jardin.
+narrateur|Ils ont joué avec le seau bleu.
+narrateur|Ils ont gardé le coquillage.
+narrateur|Le trou du coquillage laisse encore le ciel.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr"/>
@@ -9176,7 +9720,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Tom range le seau bleu. Léa reste près de le jardin. Un ballon s'immobilise. Tom chuchote : c'est fini. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Tom dit merci à maman.</t>
+          <t>Le galet est lisse, tout gris. Il sent encore la mer. On le pose ensemble ? Oui. Sarah pose le galet, tout doux. On invite. On joue ensemble. Bravo, Aniss. C'est du bon travail. Le galet tapote l'anse du seau. On est encore dans le jardin. Le seau bleu est rangé, presque. Vous jouez encore ensemble ? Oui. Oui. Bravo. Les tailles sont différentes. On joue ensemble. Aniss pose le galet, tout doux.</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -9316,7 +9860,25 @@
       <c r="AV48" s="2" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>narrateur|Tom range le seau bleu. Léa reste près de le jardin. Un ballon s'immobilise. Tom chuchote : c'est fini. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Tom dit merci à maman.</t>
+          <t>narrateur|Le galet est lisse, tout gris.
+narrateur|Il sent encore la mer.
+enfant-m|On le pose ensemble ?
+enfant-f|Oui.
+narrateur|Sarah pose le galet, tout doux.
+papa|On invite.
+papa|On joue ensemble.
+maman|Bravo, Aniss.
+maman|C'est du bon travail.
+narrateur|Le galet tapote l'anse du seau.
+narrateur|On est encore dans le jardin.
+narrateur|Le seau bleu est rangé, presque.
+papa|Vous jouez encore ensemble ?
+enfant-m|Oui.
+enfant-f|Oui.
+maman|Bravo.
+maman|Les tailles sont différentes.
+maman|On joue ensemble.
+narrateur|Aniss pose le galet, tout doux.</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr"/>
@@ -9344,7 +9906,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a joué ensemble. Oui. Bravo, Aniss. Tu as invité Sarah. Aniss a vécu dans le jardin. Ils ont joué avec le seau bleu. Ils ont gardé le galet. Le galet reste lisse, tout calme. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -9484,7 +10046,15 @@
       <c r="AV49" s="2" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|On a joué ensemble.
+enfant-f|Oui.
+maman|Bravo, Aniss.
+papa|Tu as invité Sarah.
+narrateur|Aniss a vécu dans le jardin.
+narrateur|Ils ont joué avec le seau bleu.
+narrateur|Ils ont gardé le galet.
+narrateur|Le galet reste lisse, tout calme.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr"/>
@@ -9512,7 +10082,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Sami est là. le seau bleu aussi. le jardin reste dans le souvenir. Une feuille tombe. Tom ferme le sac. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Tom dit merci à maman.</t>
+          <t>Le filet sent le sel, un peu. Sarah le tient, tout haut. Aniss tient un bout, plus bas. On tire doucement ? Oui. Les tailles sont différentes. On peut jouer ensemble. Bravo. Vous jouez ensemble. Le filet s'égoutte dans le seau bleu. On est encore dans le jardin. Le seau bleu est rangé, presque. Vous jouez encore ensemble ? Oui. Oui. Bravo. Les tailles sont différentes. On joue ensemble. Aniss pose le filet, tout doux.</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -9652,7 +10222,25 @@
       <c r="AV50" s="2" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>narrateur|Sami est là. le seau bleu aussi. le jardin reste dans le souvenir. Une feuille tombe. Tom ferme le sac. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Tom dit merci à maman.</t>
+          <t>narrateur|Le filet sent le sel, un peu.
+narrateur|Sarah le tient, tout haut.
+narrateur|Aniss tient un bout, plus bas.
+enfant-m|On tire doucement ?
+enfant-f|Oui.
+maman|Les tailles sont différentes.
+maman|On peut jouer ensemble.
+papa|Bravo.
+papa|Vous jouez ensemble.
+narrateur|Le filet s'égoutte dans le seau bleu.
+narrateur|On est encore dans le jardin.
+narrateur|Le seau bleu est rangé, presque.
+papa|Vous jouez encore ensemble ?
+enfant-m|Oui.
+enfant-f|Oui.
+maman|Bravo.
+maman|Les tailles sont différentes.
+maman|On joue ensemble.
+narrateur|Aniss pose le filet, tout doux.</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr"/>
@@ -9680,7 +10268,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a joué ensemble. Oui. Bravo, Aniss. Tu as invité Sarah. Aniss a vécu dans le jardin. Ils ont joué avec le seau bleu. Ils ont gardé le filet. Le filet sent encore le sel, tout loin. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -9820,7 +10408,15 @@
       <c r="AV51" s="2" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|On a joué ensemble.
+enfant-f|Oui.
+maman|Bravo, Aniss.
+papa|Tu as invité Sarah.
+narrateur|Aniss a vécu dans le jardin.
+narrateur|Ils ont joué avec le seau bleu.
+narrateur|Ils ont gardé le filet.
+narrateur|Le filet sent encore le sel, tout loin.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr"/>
@@ -9848,7 +10444,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Tom assoit le doudou sous un linge. Un copain d'une autre taille l'abrite. Maman montre le geste, lentement. Les tailles sont différentes. On joue ensemble. On peut jouer ensemble.</t>
+          <t>Aniss pose le doudou. Le tissu est encore sablé. Tu le caresses ? Oui. Sarah est plus grande. Sa main couvre presque le doudou. La main d'Aniss est plus petite. On invite. On joue ensemble. Bravo, Aniss. Tu as invité Sarah. Le doudou a une oreille froissée. Le doudou s'abrite sous le linge. On est encore dans le jardin. On invite. On joue ensemble.</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -9988,7 +10584,22 @@
       <c r="AV52" s="2" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>narrateur|Tom assoit le doudou sous un linge. Un copain d'une autre taille l'abrite. Maman montre le geste, lentement. Les tailles sont différentes. On joue ensemble. On peut jouer ensemble.</t>
+          <t>narrateur|Aniss pose le doudou.
+narrateur|Le tissu est encore sablé.
+enfant-m|Tu le caresses ?
+enfant-f|Oui.
+narrateur|Sarah est plus grande.
+narrateur|Sa main couvre presque le doudou.
+narrateur|La main d'Aniss est plus petite.
+maman|On invite.
+maman|On joue ensemble.
+papa|Bravo, Aniss.
+papa|Tu as invité Sarah.
+narrateur|Le doudou a une oreille froissée.
+narrateur|Le doudou s'abrite sous le linge.
+narrateur|On est encore dans le jardin.
+maman|On invite.
+maman|On joue ensemble.</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr"/>
@@ -10016,7 +10627,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Trois souvenirs de mer attendent. Le coquillage, le galet, ou le filet ? On joue encore ensemble.</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -10184,7 +10795,9 @@
       </c>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|Trois souvenirs de mer attendent.
+papa|Le coquillage, le galet, ou le filet ?
+maman|On joue encore ensemble.</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr"/>
@@ -10212,7 +10825,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Tom rejoint Tom. le doudou est rangé. le jardin est fini. Une chaussette est encore sablée. Tom ferme la porte, tout doux. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Tom dit merci à maman.</t>
+          <t>Le coquillage a encore un trou. Aniss le tend à Sarah. Tu regardes ? Oui. Sarah le lève, tout haut. Aniss le voit, plus bas. Les tailles sont différentes. On joue ensemble. Bravo. Tu as invité. Le coquillage se cache sous le doudou. On est encore dans le jardin. Le doudou est rangé, presque. Vous jouez encore ensemble ? Oui. Oui. Bravo. Les tailles sont différentes. On joue ensemble. Aniss pose le coquillage, tout doux.</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -10352,7 +10965,26 @@
       <c r="AV54" s="2" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>narrateur|Tom rejoint Tom. le doudou est rangé. le jardin est fini. Une chaussette est encore sablée. Tom ferme la porte, tout doux. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Tom dit merci à maman.</t>
+          <t>narrateur|Le coquillage a encore un trou.
+narrateur|Aniss le tend à Sarah.
+enfant-m|Tu regardes ?
+enfant-f|Oui.
+narrateur|Sarah le lève, tout haut.
+narrateur|Aniss le voit, plus bas.
+maman|Les tailles sont différentes.
+maman|On joue ensemble.
+papa|Bravo.
+papa|Tu as invité.
+narrateur|Le coquillage se cache sous le doudou.
+narrateur|On est encore dans le jardin.
+narrateur|Le doudou est rangé, presque.
+papa|Vous jouez encore ensemble ?
+enfant-m|Oui.
+enfant-f|Oui.
+maman|Bravo.
+maman|Les tailles sont différentes.
+maman|On joue ensemble.
+narrateur|Aniss pose le coquillage, tout doux.</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr"/>
@@ -10380,7 +11012,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a joué ensemble. Oui. Bravo, Aniss. Tu as invité Sarah. Aniss a vécu dans le jardin. Ils ont joué avec le doudou. Ils ont gardé le coquillage. Le trou du coquillage laisse encore le ciel. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -10520,7 +11152,15 @@
       <c r="AV55" s="2" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|On a joué ensemble.
+enfant-f|Oui.
+maman|Bravo, Aniss.
+papa|Tu as invité Sarah.
+narrateur|Aniss a vécu dans le jardin.
+narrateur|Ils ont joué avec le doudou.
+narrateur|Ils ont gardé le coquillage.
+narrateur|Le trou du coquillage laisse encore le ciel.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr"/>
@@ -10548,7 +11188,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Près de Léa. Tom pose le doudou. le jardin est derrière. On écoute jusqu'au bout. Tom écoute maman encore une fois. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Tom dit merci à maman.</t>
+          <t>Le galet est lisse, tout gris. Il sent encore la mer. On le pose ensemble ? Oui. Sarah pose le galet, tout doux. On invite. On joue ensemble. Bravo, Aniss. C'est du bon travail. Le galet pèse sur le doudou, tout léger. On est encore dans le jardin. Le doudou est rangé, presque. Vous jouez encore ensemble ? Oui. Oui. Bravo. Les tailles sont différentes. On joue ensemble. Aniss pose le galet, tout doux.</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -10688,7 +11328,25 @@
       <c r="AV56" s="2" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>narrateur|Près de Léa. Tom pose le doudou. le jardin est derrière. On écoute jusqu'au bout. Tom écoute maman encore une fois. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Tom dit merci à maman.</t>
+          <t>narrateur|Le galet est lisse, tout gris.
+narrateur|Il sent encore la mer.
+enfant-m|On le pose ensemble ?
+enfant-f|Oui.
+narrateur|Sarah pose le galet, tout doux.
+papa|On invite.
+papa|On joue ensemble.
+maman|Bravo, Aniss.
+maman|C'est du bon travail.
+narrateur|Le galet pèse sur le doudou, tout léger.
+narrateur|On est encore dans le jardin.
+narrateur|Le doudou est rangé, presque.
+papa|Vous jouez encore ensemble ?
+enfant-m|Oui.
+enfant-f|Oui.
+maman|Bravo.
+maman|Les tailles sont différentes.
+maman|On joue ensemble.
+narrateur|Aniss pose le galet, tout doux.</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr"/>
@@ -10716,7 +11374,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a joué ensemble. Oui. Bravo, Aniss. Tu as invité Sarah. Aniss a vécu dans le jardin. Ils ont joué avec le doudou. Ils ont gardé le galet. Le galet reste lisse, tout calme. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -10856,7 +11514,15 @@
       <c r="AV57" s="2" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|On a joué ensemble.
+enfant-f|Oui.
+maman|Bravo, Aniss.
+papa|Tu as invité Sarah.
+narrateur|Aniss a vécu dans le jardin.
+narrateur|Ils ont joué avec le doudou.
+narrateur|Ils ont gardé le galet.
+narrateur|Le galet reste lisse, tout calme.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr"/>
@@ -10884,7 +11550,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Tom montre Sami. Maman a vu le jardin. Et le doudou. On range un objet. Tom plie un pull. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Tom dit merci à maman.</t>
+          <t>Le filet sent le sel, un peu. Sarah le tient, tout haut. Aniss tient un bout, plus bas. On tire doucement ? Oui. Les tailles sont différentes. On peut jouer ensemble. Bravo. Vous jouez ensemble. Le filet abrite le doudou, au soleil. On est encore dans le jardin. Le doudou est rangé, presque. Vous jouez encore ensemble ? Oui. Oui. Bravo. Les tailles sont différentes. On joue ensemble. Aniss pose le filet, tout doux.</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -11024,7 +11690,25 @@
       <c r="AV58" s="2" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>narrateur|Tom montre Sami. Maman a vu le jardin. Et le doudou. On range un objet. Tom plie un pull. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Tom dit merci à maman.</t>
+          <t>narrateur|Le filet sent le sel, un peu.
+narrateur|Sarah le tient, tout haut.
+narrateur|Aniss tient un bout, plus bas.
+enfant-m|On tire doucement ?
+enfant-f|Oui.
+maman|Les tailles sont différentes.
+maman|On peut jouer ensemble.
+papa|Bravo.
+papa|Vous jouez ensemble.
+narrateur|Le filet abrite le doudou, au soleil.
+narrateur|On est encore dans le jardin.
+narrateur|Le doudou est rangé, presque.
+papa|Vous jouez encore ensemble ?
+enfant-m|Oui.
+enfant-f|Oui.
+maman|Bravo.
+maman|Les tailles sont différentes.
+maman|On joue ensemble.
+narrateur|Aniss pose le filet, tout doux.</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr"/>
@@ -11052,7 +11736,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a joué ensemble. Oui. Bravo, Aniss. Tu as invité Sarah. Aniss a vécu dans le jardin. Ils ont joué avec le doudou. Ils ont gardé le filet. Le filet sent encore le sel, tout loin. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -11192,7 +11876,15 @@
       <c r="AV59" s="2" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|On a joué ensemble.
+enfant-f|Oui.
+maman|Bravo, Aniss.
+papa|Tu as invité Sarah.
+narrateur|Aniss a vécu dans le jardin.
+narrateur|Ils ont joué avec le doudou.
+narrateur|Ils ont gardé le filet.
+narrateur|Le filet sent encore le sel, tout loin.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr"/>
@@ -11220,7 +11912,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Après la mer, Tom va dans la chambre. La couverture est douce. Un copain d'une autre taille pose un galet. Tom l'invite. Ils font un bateau avec l'oreiller. Ils jouent ensemble. Les tailles sont différentes. On peut jouer ensemble.</t>
+          <t>Après la mer, la chambre est calme. La couverture est douce. Un oreiller devient un bateau. Sarah pose un galet, tout haut. Aniss pose le coquillage, plus bas. Les tailles sont différentes. Tu viens sur le bateau ? Oui. On invite. On joue ensemble. Bravo, Aniss. Tu as invité Sarah. Ils poussent l'oreiller, tout doux. La mer chante encore. Un rayon pose sur le plaid.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -11360,7 +12052,21 @@
       <c r="AV60" s="2" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>narrateur|Après la mer, Tom va dans la chambre. La couverture est douce. Un copain d'une autre taille pose un galet. Tom l'invite. Ils font un bateau avec l'oreiller. Ils jouent ensemble. Les tailles sont différentes. On peut jouer ensemble.</t>
+          <t>narrateur|Après la mer, la chambre est calme.
+narrateur|La couverture est douce.
+narrateur|Un oreiller devient un bateau.
+narrateur|Sarah pose un galet, tout haut.
+narrateur|Aniss pose le coquillage, plus bas.
+narrateur|Les tailles sont différentes.
+enfant-m|Tu viens sur le bateau ?
+enfant-f|Oui.
+papa|On invite.
+papa|On joue ensemble.
+maman|Bravo, Aniss.
+maman|Tu as invité Sarah.
+narrateur|Ils poussent l'oreiller, tout doux.
+enfant-f|La mer chante encore.
+narrateur|Un rayon pose sur le plaid.</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr"/>
@@ -11388,7 +12094,7 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>On invite, et on joue ensemble ?</t>
+          <t>Aniss a invité Sarah. On joue ensemble ?</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
@@ -11544,7 +12250,8 @@
       </c>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>narrateur|On invite, et on joue ensemble ?</t>
+          <t>narrateur|Aniss a invité Sarah.
+maman|On joue ensemble ?</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr"/>
@@ -11572,7 +12279,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Oui. On joue ensemble. Tom hoche la tête. On continue, avec maman. Les tailles sont différentes. On joue ensemble. On peut jouer ensemble.</t>
+          <t>Oui. On invite. On joue ensemble. Aniss hoche la tête. On joue. Bravo. Tu as fait du bon travail. Le bateau-oreiller s'arrête, tout doux. Le rayon glisse encore.</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -11716,7 +12423,15 @@
       </c>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>narrateur|Oui. On joue ensemble. Tom hoche la tête. On continue, avec maman. Les tailles sont différentes. On joue ensemble. On peut jouer ensemble.</t>
+          <t>maman|Oui.
+maman|On invite.
+maman|On joue ensemble.
+narrateur|Aniss hoche la tête.
+enfant-m|On joue.
+papa|Bravo.
+papa|Tu as fait du bon travail.
+narrateur|Le bateau-oreiller s'arrête, tout doux.
+narrateur|Le rayon glisse encore.</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr"/>
@@ -11744,7 +12459,7 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+          <t>Trois jeux attendent, tout proches. Le ballon rouge, le seau bleu, ou le doudou ? On invite. On joue ensemble.</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
@@ -11908,7 +12623,10 @@
       <c r="AV63" s="2" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+          <t>narrateur|Trois jeux attendent, tout proches.
+maman|Le ballon rouge, le seau bleu, ou le doudou ?
+papa|On invite.
+papa|On joue ensemble.</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr"/>
@@ -11936,7 +12654,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Tom fait un bateau : le ballon rouge est le phare. Un copain plus grand tient l'oreiller. Maman reste tout près. Les tailles sont différentes. On joue ensemble. On peut jouer ensemble.</t>
+          <t>Aniss pose le ballon rouge. Le ballon est un peu sablé. Tu veux jouer ? Oui. Sarah est plus grande. Elle rattrape le ballon, tout haut. Aniss le pousse, plus bas. Les tailles sont différentes. On joue ensemble. Bravo, Aniss. Tu as invité. Le ballon roule, tout doux. Le ballon rouge devient un phare. On est encore dans la chambre. On invite. On joue ensemble.</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -12076,10 +12794,29 @@
       <c r="AV64" s="2" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>narrateur|Tom fait un bateau : le ballon rouge est le phare. Un copain plus grand tient l'oreiller. Maman reste tout près. Les tailles sont différentes. On joue ensemble. On peut jouer ensemble.</t>
-        </is>
-      </c>
-      <c r="AX64" t="inlineStr"/>
+          <t>narrateur|Aniss pose le ballon rouge.
+narrateur|Le ballon est un peu sablé.
+enfant-m|Tu veux jouer ?
+enfant-f|Oui.
+narrateur|Sarah est plus grande.
+narrateur|Elle rattrape le ballon, tout haut.
+narrateur|Aniss le pousse, plus bas.
+maman|Les tailles sont différentes.
+maman|On joue ensemble.
+papa|Bravo, Aniss.
+papa|Tu as invité.
+narrateur|Le ballon roule, tout doux.
+narrateur|Le ballon rouge devient un phare.
+narrateur|On est encore dans la chambre.
+maman|On invite.
+maman|On joue ensemble.</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>ballon</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12104,7 +12841,7 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Trois souvenirs de mer attendent. Le coquillage, le galet, ou le filet ? On joue encore ensemble.</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
@@ -12272,7 +13009,9 @@
       </c>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|Trois souvenirs de mer attendent.
+papa|Le coquillage, le galet, ou le filet ?
+maman|On joue encore ensemble.</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr"/>
@@ -12300,7 +13039,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Tom a choisi la chambre. Puis le ballon rouge. Puis Tom. On entend un oiseau. Tom raccroche un linge. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Tom dit merci à maman.</t>
+          <t>Le coquillage a encore un trou. Aniss le tend à Sarah. Tu regardes ? Oui. Sarah le lève, tout haut. Aniss le voit, plus bas. Les tailles sont différentes. On joue ensemble. Bravo. Tu as invité. Le coquillage est le trésor du phare. On est encore dans la chambre. Le ballon rouge est rangé, presque. Vous jouez encore ensemble ? Oui. Oui. Bravo. Les tailles sont différentes. On joue ensemble. Aniss pose le coquillage, tout doux.</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -12440,7 +13179,26 @@
       <c r="AV66" s="2" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>narrateur|Tom a choisi la chambre. Puis le ballon rouge. Puis Tom. On entend un oiseau. Tom raccroche un linge. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Tom dit merci à maman.</t>
+          <t>narrateur|Le coquillage a encore un trou.
+narrateur|Aniss le tend à Sarah.
+enfant-m|Tu regardes ?
+enfant-f|Oui.
+narrateur|Sarah le lève, tout haut.
+narrateur|Aniss le voit, plus bas.
+maman|Les tailles sont différentes.
+maman|On joue ensemble.
+papa|Bravo.
+papa|Tu as invité.
+narrateur|Le coquillage est le trésor du phare.
+narrateur|On est encore dans la chambre.
+narrateur|Le ballon rouge est rangé, presque.
+papa|Vous jouez encore ensemble ?
+enfant-m|Oui.
+enfant-f|Oui.
+maman|Bravo.
+maman|Les tailles sont différentes.
+maman|On joue ensemble.
+narrateur|Aniss pose le coquillage, tout doux.</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr"/>
@@ -12468,7 +13226,7 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a joué ensemble. Oui. Bravo, Aniss. Tu as invité Sarah. Aniss a vécu dans la chambre. Ils ont joué avec le ballon rouge. Ils ont gardé le coquillage. Le trou du coquillage laisse encore le ciel. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
@@ -12608,7 +13366,15 @@
       <c r="AV67" s="2" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|On a joué ensemble.
+enfant-f|Oui.
+maman|Bravo, Aniss.
+papa|Tu as invité Sarah.
+narrateur|Aniss a vécu dans la chambre.
+narrateur|Ils ont joué avec le ballon rouge.
+narrateur|Ils ont gardé le coquillage.
+narrateur|Le trou du coquillage laisse encore le ciel.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr"/>
@@ -12636,7 +13402,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Tom s'arrête près de Léa. le ballon rouge est rangé. On rit un peu. Tom dit merci à maman. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Tom dit merci à maman.</t>
+          <t>Le galet est lisse, tout gris. Il sent encore la mer. On le pose ensemble ? Oui. Sarah pose le galet, tout doux. On invite. On joue ensemble. Bravo, Aniss. C'est du bon travail. Le galet ancre le bateau-oreiller. On est encore dans la chambre. Le ballon rouge est rangé, presque. Vous jouez encore ensemble ? Oui. Oui. Bravo. Les tailles sont différentes. On joue ensemble. Aniss pose le galet, tout doux.</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -12776,7 +13542,25 @@
       <c r="AV68" s="2" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>narrateur|Tom s'arrête près de Léa. le ballon rouge est rangé. On rit un peu. Tom dit merci à maman. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Tom dit merci à maman.</t>
+          <t>narrateur|Le galet est lisse, tout gris.
+narrateur|Il sent encore la mer.
+enfant-m|On le pose ensemble ?
+enfant-f|Oui.
+narrateur|Sarah pose le galet, tout doux.
+papa|On invite.
+papa|On joue ensemble.
+maman|Bravo, Aniss.
+maman|C'est du bon travail.
+narrateur|Le galet ancre le bateau-oreiller.
+narrateur|On est encore dans la chambre.
+narrateur|Le ballon rouge est rangé, presque.
+papa|Vous jouez encore ensemble ?
+enfant-m|Oui.
+enfant-f|Oui.
+maman|Bravo.
+maman|Les tailles sont différentes.
+maman|On joue ensemble.
+narrateur|Aniss pose le galet, tout doux.</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr"/>
@@ -12804,7 +13588,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a joué ensemble. Oui. Bravo, Aniss. Tu as invité Sarah. Aniss a vécu dans la chambre. Ils ont joué avec le ballon rouge. Ils ont gardé le galet. Le galet reste lisse, tout calme. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -12944,7 +13728,15 @@
       <c r="AV69" s="2" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|On a joué ensemble.
+enfant-f|Oui.
+maman|Bravo, Aniss.
+papa|Tu as invité Sarah.
+narrateur|Aniss a vécu dans la chambre.
+narrateur|Ils ont joué avec le ballon rouge.
+narrateur|Ils ont gardé le galet.
+narrateur|Le galet reste lisse, tout calme.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr"/>
@@ -12972,7 +13764,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Tom se souvient de la chambre. Et de le ballon rouge. Et de Sami. On dit merci. Tom souffle, puis sourit à maman. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Tom dit merci à maman.</t>
+          <t>Le filet sent le sel, un peu. Sarah le tient, tout haut. Aniss tient un bout, plus bas. On tire doucement ? Oui. Les tailles sont différentes. On peut jouer ensemble. Bravo. Vous jouez ensemble. Le filet devient une voile, tout douce. On est encore dans la chambre. Le ballon rouge est rangé, presque. Vous jouez encore ensemble ? Oui. Oui. Bravo. Les tailles sont différentes. On joue ensemble. Aniss pose le filet, tout doux.</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -13112,7 +13904,25 @@
       <c r="AV70" s="2" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>narrateur|Tom se souvient de la chambre. Et de le ballon rouge. Et de Sami. On dit merci. Tom souffle, puis sourit à maman. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Tom dit merci à maman.</t>
+          <t>narrateur|Le filet sent le sel, un peu.
+narrateur|Sarah le tient, tout haut.
+narrateur|Aniss tient un bout, plus bas.
+enfant-m|On tire doucement ?
+enfant-f|Oui.
+maman|Les tailles sont différentes.
+maman|On peut jouer ensemble.
+papa|Bravo.
+papa|Vous jouez ensemble.
+narrateur|Le filet devient une voile, tout douce.
+narrateur|On est encore dans la chambre.
+narrateur|Le ballon rouge est rangé, presque.
+papa|Vous jouez encore ensemble ?
+enfant-m|Oui.
+enfant-f|Oui.
+maman|Bravo.
+maman|Les tailles sont différentes.
+maman|On joue ensemble.
+narrateur|Aniss pose le filet, tout doux.</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr"/>
@@ -13140,7 +13950,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a joué ensemble. Oui. Bravo, Aniss. Tu as invité Sarah. Aniss a vécu dans la chambre. Ils ont joué avec le ballon rouge. Ils ont gardé le filet. Le filet sent encore le sel, tout loin. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -13280,7 +14090,15 @@
       <c r="AV71" s="2" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|On a joué ensemble.
+enfant-f|Oui.
+maman|Bravo, Aniss.
+papa|Tu as invité Sarah.
+narrateur|Aniss a vécu dans la chambre.
+narrateur|Ils ont joué avec le ballon rouge.
+narrateur|Ils ont gardé le filet.
+narrateur|Le filet sent encore le sel, tout loin.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr"/>
@@ -13308,7 +14126,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Tom cache le seau bleu derrière le lit. Un copain plus petit le retrouve. Maman montre le geste, lentement. Les tailles sont différentes. On joue ensemble. On peut jouer ensemble.</t>
+          <t>Aniss prend le seau bleu. L'anse est un peu rêche. On le tient ensemble ? Oui. Sarah tient l'anse, tout haut. Aniss tient le bord, plus bas. Les tailles sont différentes. On peut jouer ensemble. Bravo. Vous jouez ensemble. Un peu d'eau tremble, dans le seau. Le seau bleu se cache derrière le lit. On est encore dans la chambre. On invite. On joue ensemble.</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -13448,10 +14266,28 @@
       <c r="AV72" s="2" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>narrateur|Tom cache le seau bleu derrière le lit. Un copain plus petit le retrouve. Maman montre le geste, lentement. Les tailles sont différentes. On joue ensemble. On peut jouer ensemble.</t>
-        </is>
-      </c>
-      <c r="AX72" t="inlineStr"/>
+          <t>narrateur|Aniss prend le seau bleu.
+narrateur|L'anse est un peu rêche.
+enfant-m|On le tient ensemble ?
+enfant-f|Oui.
+narrateur|Sarah tient l'anse, tout haut.
+narrateur|Aniss tient le bord, plus bas.
+papa|Les tailles sont différentes.
+papa|On peut jouer ensemble.
+maman|Bravo.
+maman|Vous jouez ensemble.
+narrateur|Un peu d'eau tremble, dans le seau.
+narrateur|Le seau bleu se cache derrière le lit.
+narrateur|On est encore dans la chambre.
+maman|On invite.
+maman|On joue ensemble.</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13476,7 +14312,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Trois souvenirs de mer attendent. Le coquillage, le galet, ou le filet ? On joue encore ensemble.</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -13644,7 +14480,9 @@
       </c>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|Trois souvenirs de mer attendent.
+papa|Le coquillage, le galet, ou le filet ?
+maman|On joue encore ensemble.</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr"/>
@@ -13672,7 +14510,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Avec Tom. Après le seau bleu. Près de la chambre. Tom s'arrête. Les chaussures font toc toc. Tom serre la main de maman. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Tom dit merci à maman.</t>
+          <t>Le coquillage a encore un trou. Aniss le tend à Sarah. Tu regardes ? Oui. Sarah le lève, tout haut. Aniss le voit, plus bas. Les tailles sont différentes. On joue ensemble. Bravo. Tu as invité. Le coquillage revient du seau caché. On est encore dans la chambre. Le seau bleu est rangé, presque. Vous jouez encore ensemble ? Oui. Oui. Bravo. Les tailles sont différentes. On joue ensemble. Aniss pose le coquillage, tout doux.</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -13812,7 +14650,26 @@
       <c r="AV74" s="2" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>narrateur|Avec Tom. Après le seau bleu. Près de la chambre. Tom s'arrête. Les chaussures font toc toc. Tom serre la main de maman. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Tom dit merci à maman.</t>
+          <t>narrateur|Le coquillage a encore un trou.
+narrateur|Aniss le tend à Sarah.
+enfant-m|Tu regardes ?
+enfant-f|Oui.
+narrateur|Sarah le lève, tout haut.
+narrateur|Aniss le voit, plus bas.
+maman|Les tailles sont différentes.
+maman|On joue ensemble.
+papa|Bravo.
+papa|Tu as invité.
+narrateur|Le coquillage revient du seau caché.
+narrateur|On est encore dans la chambre.
+narrateur|Le seau bleu est rangé, presque.
+papa|Vous jouez encore ensemble ?
+enfant-m|Oui.
+enfant-f|Oui.
+maman|Bravo.
+maman|Les tailles sont différentes.
+maman|On joue ensemble.
+narrateur|Aniss pose le coquillage, tout doux.</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr"/>
@@ -13840,7 +14697,7 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a joué ensemble. Oui. Bravo, Aniss. Tu as invité Sarah. Aniss a vécu dans la chambre. Ils ont joué avec le seau bleu. Ils ont gardé le coquillage. Le trou du coquillage laisse encore le ciel. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -13980,7 +14837,15 @@
       <c r="AV75" s="2" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|On a joué ensemble.
+enfant-f|Oui.
+maman|Bravo, Aniss.
+papa|Tu as invité Sarah.
+narrateur|Aniss a vécu dans la chambre.
+narrateur|Ils ont joué avec le seau bleu.
+narrateur|Ils ont gardé le coquillage.
+narrateur|Le trou du coquillage laisse encore le ciel.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr"/>
@@ -14008,7 +14873,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Tom range le seau bleu. Léa reste près de la chambre. On souffle doucement. Tom sourit. Maman sourit aussi. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Tom dit merci à maman.</t>
+          <t>Le galet est lisse, tout gris. Il sent encore la mer. On le pose ensemble ? Oui. Sarah pose le galet, tout doux. On invite. On joue ensemble. Bravo, Aniss. C'est du bon travail. Le galet roule derrière le lit. On est encore dans la chambre. Le seau bleu est rangé, presque. Vous jouez encore ensemble ? Oui. Oui. Bravo. Les tailles sont différentes. On joue ensemble. Aniss pose le galet, tout doux.</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -14148,7 +15013,25 @@
       <c r="AV76" s="2" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>narrateur|Tom range le seau bleu. Léa reste près de la chambre. On souffle doucement. Tom sourit. Maman sourit aussi. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Tom dit merci à maman.</t>
+          <t>narrateur|Le galet est lisse, tout gris.
+narrateur|Il sent encore la mer.
+enfant-m|On le pose ensemble ?
+enfant-f|Oui.
+narrateur|Sarah pose le galet, tout doux.
+papa|On invite.
+papa|On joue ensemble.
+maman|Bravo, Aniss.
+maman|C'est du bon travail.
+narrateur|Le galet roule derrière le lit.
+narrateur|On est encore dans la chambre.
+narrateur|Le seau bleu est rangé, presque.
+papa|Vous jouez encore ensemble ?
+enfant-m|Oui.
+enfant-f|Oui.
+maman|Bravo.
+maman|Les tailles sont différentes.
+maman|On joue ensemble.
+narrateur|Aniss pose le galet, tout doux.</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr"/>
@@ -14176,7 +15059,7 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a joué ensemble. Oui. Bravo, Aniss. Tu as invité Sarah. Aniss a vécu dans la chambre. Ils ont joué avec le seau bleu. Ils ont gardé le galet. Le galet reste lisse, tout calme. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -14316,7 +15199,15 @@
       <c r="AV77" s="2" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|On a joué ensemble.
+enfant-f|Oui.
+maman|Bravo, Aniss.
+papa|Tu as invité Sarah.
+narrateur|Aniss a vécu dans la chambre.
+narrateur|Ils ont joué avec le seau bleu.
+narrateur|Ils ont gardé le galet.
+narrateur|Le galet reste lisse, tout calme.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr"/>
@@ -14344,7 +15235,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Sami est là. le seau bleu aussi. la chambre reste dans le souvenir. Le savon sent bon. Tom boit une gorgée d'eau. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Tom dit merci à maman.</t>
+          <t>Le filet sent le sel, un peu. Sarah le tient, tout haut. Aniss tient un bout, plus bas. On tire doucement ? Oui. Les tailles sont différentes. On peut jouer ensemble. Bravo. Vous jouez ensemble. Le filet sort du seau, tout salé. On est encore dans la chambre. Le seau bleu est rangé, presque. Vous jouez encore ensemble ? Oui. Oui. Bravo. Les tailles sont différentes. On joue ensemble. Aniss pose le filet, tout doux.</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -14484,7 +15375,25 @@
       <c r="AV78" s="2" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>narrateur|Sami est là. le seau bleu aussi. la chambre reste dans le souvenir. Le savon sent bon. Tom boit une gorgée d'eau. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Tom dit merci à maman.</t>
+          <t>narrateur|Le filet sent le sel, un peu.
+narrateur|Sarah le tient, tout haut.
+narrateur|Aniss tient un bout, plus bas.
+enfant-m|On tire doucement ?
+enfant-f|Oui.
+maman|Les tailles sont différentes.
+maman|On peut jouer ensemble.
+papa|Bravo.
+papa|Vous jouez ensemble.
+narrateur|Le filet sort du seau, tout salé.
+narrateur|On est encore dans la chambre.
+narrateur|Le seau bleu est rangé, presque.
+papa|Vous jouez encore ensemble ?
+enfant-m|Oui.
+enfant-f|Oui.
+maman|Bravo.
+maman|Les tailles sont différentes.
+maman|On joue ensemble.
+narrateur|Aniss pose le filet, tout doux.</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr"/>
@@ -14512,7 +15421,7 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a joué ensemble. Oui. Bravo, Aniss. Tu as invité Sarah. Aniss a vécu dans la chambre. Ils ont joué avec le seau bleu. Ils ont gardé le filet. Le filet sent encore le sel, tout loin. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
@@ -14652,7 +15561,15 @@
       <c r="AV79" s="2" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|On a joué ensemble.
+enfant-f|Oui.
+maman|Bravo, Aniss.
+papa|Tu as invité Sarah.
+narrateur|Aniss a vécu dans la chambre.
+narrateur|Ils ont joué avec le seau bleu.
+narrateur|Ils ont gardé le filet.
+narrateur|Le filet sent encore le sel, tout loin.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr"/>
@@ -14680,7 +15597,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Tom calce le doudou sous la couverture. Un copain d'une autre taille chuchote. Je suis là. Les tailles sont différentes. On joue ensemble. On peut jouer ensemble.</t>
+          <t>Aniss pose le doudou. Le tissu est encore sablé. Tu le caresses ? Oui. Sarah est plus grande. Sa main couvre presque le doudou. La main d'Aniss est plus petite. On invite. On joue ensemble. Bravo, Aniss. Tu as invité Sarah. Le doudou a une oreille froissée. Le doudou se cale sous la couverture. On est encore dans la chambre. On invite. On joue ensemble.</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -14820,9 +15737,22 @@
       <c r="AV80" s="2" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>narrateur|Tom calce le doudou sous la couverture. Un copain d'une autre taille chuchote.
-maman|Je suis là.
-narrateur|Les tailles sont différentes. On joue ensemble. On peut jouer ensemble.</t>
+          <t>narrateur|Aniss pose le doudou.
+narrateur|Le tissu est encore sablé.
+enfant-m|Tu le caresses ?
+enfant-f|Oui.
+narrateur|Sarah est plus grande.
+narrateur|Sa main couvre presque le doudou.
+narrateur|La main d'Aniss est plus petite.
+maman|On invite.
+maman|On joue ensemble.
+papa|Bravo, Aniss.
+papa|Tu as invité Sarah.
+narrateur|Le doudou a une oreille froissée.
+narrateur|Le doudou se cale sous la couverture.
+narrateur|On est encore dans la chambre.
+maman|On invite.
+maman|On joue ensemble.</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr"/>
@@ -14850,7 +15780,7 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Trois souvenirs de mer attendent. Le coquillage, le galet, ou le filet ? On joue encore ensemble.</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
@@ -15018,7 +15948,9 @@
       </c>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|Trois souvenirs de mer attendent.
+papa|Le coquillage, le galet, ou le filet ?
+maman|On joue encore ensemble.</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr"/>
@@ -15046,7 +15978,7 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Tom rejoint Tom. le doudou est rangé. la chambre est fini. Une cloche tinte, tout loin. Tom enfile ses chaussons. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Tom dit merci à maman.</t>
+          <t>Le coquillage a encore un trou. Aniss le tend à Sarah. Tu regardes ? Oui. Sarah le lève, tout haut. Aniss le voit, plus bas. Les tailles sont différentes. On joue ensemble. Bravo. Tu as invité. Le coquillage chuchote près du doudou. On est encore dans la chambre. Le doudou est rangé, presque. Vous jouez encore ensemble ? Oui. Oui. Bravo. Les tailles sont différentes. On joue ensemble. Aniss pose le coquillage, tout doux.</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -15186,7 +16118,26 @@
       <c r="AV82" s="2" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>narrateur|Tom rejoint Tom. le doudou est rangé. la chambre est fini. Une cloche tinte, tout loin. Tom enfile ses chaussons. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Tom dit merci à maman.</t>
+          <t>narrateur|Le coquillage a encore un trou.
+narrateur|Aniss le tend à Sarah.
+enfant-m|Tu regardes ?
+enfant-f|Oui.
+narrateur|Sarah le lève, tout haut.
+narrateur|Aniss le voit, plus bas.
+maman|Les tailles sont différentes.
+maman|On joue ensemble.
+papa|Bravo.
+papa|Tu as invité.
+narrateur|Le coquillage chuchote près du doudou.
+narrateur|On est encore dans la chambre.
+narrateur|Le doudou est rangé, presque.
+papa|Vous jouez encore ensemble ?
+enfant-m|Oui.
+enfant-f|Oui.
+maman|Bravo.
+maman|Les tailles sont différentes.
+maman|On joue ensemble.
+narrateur|Aniss pose le coquillage, tout doux.</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr"/>
@@ -15214,7 +16165,7 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a joué ensemble. Oui. Bravo, Aniss. Tu as invité Sarah. Aniss a vécu dans la chambre. Ils ont joué avec le doudou. Ils ont gardé le coquillage. Le trou du coquillage laisse encore le ciel. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
@@ -15354,7 +16305,15 @@
       <c r="AV83" s="2" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|On a joué ensemble.
+enfant-f|Oui.
+maman|Bravo, Aniss.
+papa|Tu as invité Sarah.
+narrateur|Aniss a vécu dans la chambre.
+narrateur|Ils ont joué avec le doudou.
+narrateur|Ils ont gardé le coquillage.
+narrateur|Le trou du coquillage laisse encore le ciel.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr"/>
@@ -15382,7 +16341,7 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Près de Léa. Tom pose le doudou. la chambre est derrière. On se tient la main. Tom prend la main de maman. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Tom dit merci à maman.</t>
+          <t>Le galet est lisse, tout gris. Il sent encore la mer. On le pose ensemble ? Oui. Sarah pose le galet, tout doux. On invite. On joue ensemble. Bravo, Aniss. C'est du bon travail. Le galet chauffe sous la couverture. On est encore dans la chambre. Le doudou est rangé, presque. Vous jouez encore ensemble ? Oui. Oui. Bravo. Les tailles sont différentes. On joue ensemble. Aniss pose le galet, tout doux.</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -15522,7 +16481,25 @@
       <c r="AV84" s="2" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>narrateur|Près de Léa. Tom pose le doudou. la chambre est derrière. On se tient la main. Tom prend la main de maman. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Tom dit merci à maman.</t>
+          <t>narrateur|Le galet est lisse, tout gris.
+narrateur|Il sent encore la mer.
+enfant-m|On le pose ensemble ?
+enfant-f|Oui.
+narrateur|Sarah pose le galet, tout doux.
+papa|On invite.
+papa|On joue ensemble.
+maman|Bravo, Aniss.
+maman|C'est du bon travail.
+narrateur|Le galet chauffe sous la couverture.
+narrateur|On est encore dans la chambre.
+narrateur|Le doudou est rangé, presque.
+papa|Vous jouez encore ensemble ?
+enfant-m|Oui.
+enfant-f|Oui.
+maman|Bravo.
+maman|Les tailles sont différentes.
+maman|On joue ensemble.
+narrateur|Aniss pose le galet, tout doux.</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr"/>
@@ -15550,7 +16527,7 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a joué ensemble. Oui. Bravo, Aniss. Tu as invité Sarah. Aniss a vécu dans la chambre. Ils ont joué avec le doudou. Ils ont gardé le galet. Le galet reste lisse, tout calme. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
@@ -15690,7 +16667,15 @@
       <c r="AV85" s="2" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|On a joué ensemble.
+enfant-f|Oui.
+maman|Bravo, Aniss.
+papa|Tu as invité Sarah.
+narrateur|Aniss a vécu dans la chambre.
+narrateur|Ils ont joué avec le doudou.
+narrateur|Ils ont gardé le galet.
+narrateur|Le galet reste lisse, tout calme.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr"/>
@@ -15718,7 +16703,7 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Tom montre Sami. Maman a vu la chambre. Et le doudou. La couverture est douce. Tom s'assoit près de maman. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Tom dit merci à maman.</t>
+          <t>Le filet sent le sel, un peu. Sarah le tient, tout haut. Aniss tient un bout, plus bas. On tire doucement ? Oui. Les tailles sont différentes. On peut jouer ensemble. Bravo. Vous jouez ensemble. Le filet couvre doudou et oreiller. On est encore dans la chambre. Le doudou est rangé, presque. Vous jouez encore ensemble ? Oui. Oui. Bravo. Les tailles sont différentes. On joue ensemble. Aniss pose le filet, tout doux.</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -15858,7 +16843,25 @@
       <c r="AV86" s="2" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>narrateur|Tom montre Sami. Maman a vu la chambre. Et le doudou. La couverture est douce. Tom s'assoit près de maman. Les tailles sont différentes. On joue ensemble. On invite. On joue ensemble. Tom dit merci à maman.</t>
+          <t>narrateur|Le filet sent le sel, un peu.
+narrateur|Sarah le tient, tout haut.
+narrateur|Aniss tient un bout, plus bas.
+enfant-m|On tire doucement ?
+enfant-f|Oui.
+maman|Les tailles sont différentes.
+maman|On peut jouer ensemble.
+papa|Bravo.
+papa|Vous jouez ensemble.
+narrateur|Le filet couvre doudou et oreiller.
+narrateur|On est encore dans la chambre.
+narrateur|Le doudou est rangé, presque.
+papa|Vous jouez encore ensemble ?
+enfant-m|Oui.
+enfant-f|Oui.
+maman|Bravo.
+maman|Les tailles sont différentes.
+maman|On joue ensemble.
+narrateur|Aniss pose le filet, tout doux.</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr"/>
@@ -15886,7 +16889,7 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a joué ensemble. Oui. Bravo, Aniss. Tu as invité Sarah. Aniss a vécu dans la chambre. Ils ont joué avec le doudou. Ils ont gardé le filet. Le filet sent encore le sel, tout loin. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
@@ -16026,7 +17029,15 @@
       <c r="AV87" s="2" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|On a joué ensemble.
+enfant-f|Oui.
+maman|Bravo, Aniss.
+papa|Tu as invité Sarah.
+narrateur|Aniss a vécu dans la chambre.
+narrateur|Ils ont joué avec le doudou.
+narrateur|Ils ont gardé le filet.
+narrateur|Le filet sent encore le sel, tout loin.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr"/>
@@ -16048,7 +17059,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A13"/>
+  <dimension ref="A1:A14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16142,6 +17153,13 @@
       <c r="A13" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-DIF-001.xlsx
+++ b/stories/arbres/TREE-DIF-001.xlsx
@@ -1197,17 +1197,17 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Le cri d'une mouette entre dans la cuisine. Le sable mouillé suce le bas de la porte. La maison sent le linge, et le sel. Papa pose les sandales, près du palier. Sarah va arriver, Aniss. Aniss ouvre la paume, vers le rebord. Sa coquille rose y tient, légère. Un point d'écume y reste, blanc. Il ne sèche pas. Tu l'as vue, cette petite tache ? Je veux la montrer à Sarah. Au bord de l'eau. En ce moment, des pas sonnent dehors. Aniss, me voilà. Sarah s'arrête, sans un mot. Viens, on court ! Sarah ne bouge pas. Merci, tu as vu son silence. On prépare le sac, alors ?</t>
+          <t>Le cri d'une mouette entre dans la cuisine. Le sable mouillé suce le bas de la porte. Une ombre d'aile passe sur la table. La maison sent le linge, et le sel. Papa pose les sandales, près du palier. Sarah va arriver, Aniss. Aniss ouvre la paume, vers le rebord. C'est le rebord du volet, face à l'eau. Sa coquille rose y tient, légère. Un point d'écume y reste, blanc. Il ne sèche pas. Tu l'as vue, cette petite tache ? Je veux la montrer à Sarah. Au bord de l'eau. En ce moment, des pas sonnent dehors. Aniss, me voilà. Sarah s'arrête, sans un mot. Viens, on court ! Sarah ne bouge pas. Aniss sent ça, dans sa poitrine. On va au bord, ensemble. Merci, tu as vu son silence. On prépare le sac, alors ?</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le cri d'une mouette entre dans la cuisine. Le sable mouillé suce le bas de la porte. La maison sent le linge, et le sel. Papa pose les sandales, près du palier. Sarah va arriver, Aniss. Aniss ouvre la paume, vers le rebord. Sa coquille rose y tient, légère. Un &lt;emphasis level="moderate"&gt;point d'écume&lt;/emphasis&gt; y reste, blanc. Il ne sèche pas. Tu l'as vue, cette petite tache ? Je veux la montrer à Sarah. Au bord de l'eau. En ce moment, des pas sonnent dehors. Aniss, me voilà. Sarah s'arrête, sans un mot. Viens, on court ! Sarah ne bouge pas. Merci, tu as vu son silence. On prépare le sac, alors ?&lt;/prosody&gt;&lt;break time="500ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le cri d'une mouette entre dans la cuisine. Le sable mouillé suce le bas de la porte. Une ombre d'aile passe sur la table. La maison sent le linge, et le sel. Papa pose les sandales, près du palier. Sarah va arriver, Aniss. Aniss ouvre la paume, vers le rebord. C'est le rebord du volet, face à l'eau. Sa coquille rose y tient, légère. Un &lt;emphasis level="moderate"&gt;point d'écume&lt;/emphasis&gt; y reste, blanc. Il ne sèche pas. Tu l'as vue, cette petite tache ? Je veux la montrer à Sarah. Au bord de l'eau. En ce moment, des pas sonnent dehors. Aniss, me voilà. Sarah s'arrête, sans un mot. Viens, on court ! Sarah ne bouge pas. Aniss sent ça, dans sa poitrine. On va au bord, ensemble. Merci, tu as vu son silence. On prépare le sac, alors ?&lt;/prosody&gt;&lt;break time="500ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Le cri d'une mouette entre dans la cuisine. Le sable mouillé suce le bas de la porte. La maison sent le linge, et le sel. Papa pose les sandales, près du palier. Sarah va arriver, Aniss. Aniss ouvre la paume, vers le rebord. Sa coquille rose y tient, légère. Un &lt;emphasis&gt;point d'écume&lt;/emphasis&gt; y reste, blanc. Il ne sèche pas. Tu l'as vue, cette petite tache ? Je veux la montrer à Sarah. Au bord de l'eau. En ce moment, des pas sonnent dehors. Aniss, me voilà. Sarah s'arrête, sans un mot. Viens, on court ! Sarah ne bouge pas. Merci, tu as vu son silence. On prépare le sac, alors ? [pause]</t>
+          <t>Le cri d'une mouette entre dans la cuisine. Le sable mouillé suce le bas de la porte. Une ombre d'aile passe sur la table. La maison sent le linge, et le sel. Papa pose les sandales, près du palier. Sarah va arriver, Aniss. Aniss ouvre la paume, vers le rebord. C'est le rebord du volet, face à l'eau. Sa coquille rose y tient, légère. Un &lt;emphasis&gt;point d'écume&lt;/emphasis&gt; y reste, blanc. Il ne sèche pas. Tu l'as vue, cette petite tache ? Je veux la montrer à Sarah. Au bord de l'eau. En ce moment, des pas sonnent dehors. Aniss, me voilà. Sarah s'arrête, sans un mot. Viens, on court ! Sarah ne bouge pas. Aniss sent ça, dans sa poitrine. On va au bord, ensemble. Merci, tu as vu son silence. On prépare le sac, alors ? [pause]</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr"/>
@@ -1343,10 +1343,12 @@
         <is>
           <t>narrateur|Le cri d'une mouette entre dans la cuisine.
 narrateur|Le sable mouillé suce le bas de la porte.
+narrateur|Une ombre d'aile passe sur la table.
 narrateur|La maison sent le linge, et le sel.
 narrateur|Papa pose les sandales, près du palier.
 maman|Sarah va arriver, Aniss.
 narrateur|Aniss ouvre la paume, vers le rebord.
+narrateur|C'est le rebord du volet, face à l'eau.
 narrateur|Sa coquille rose y tient, légère.
 narrateur|Un point d'écume y reste, blanc.
 enfant-m|Il ne sèche pas.
@@ -1358,6 +1360,8 @@
 narrateur|Sarah s'arrête, sans un mot.
 enfant-m|Viens, on court !
 narrateur|Sarah ne bouge pas.
+narrateur|Aniss sent ça, dans sa poitrine.
+enfant-m|On va au bord, ensemble.
 papa|Merci, tu as vu son silence.
 maman|On prépare le sac, alors ?</t>
         </is>
@@ -1391,17 +1395,17 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Le sac attend, près des sandales. Le seau, le filet, et le linge. Tu prends quoi d'abord, Aniss ?</t>
+          <t>Le sac attend, près des sandales. Le seau, le filet, et le linge. Aniss serre la coquille, puis la pose. Tu prends quoi d'abord, Aniss ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Le sac attend, près des sandales. Le seau, le filet, et le linge. Tu prends quoi d'abord, Aniss ?&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Le sac attend, près des sandales. Le seau, le filet, et le linge. Aniss serre la coquille, puis la pose. Tu prends quoi d'abord, Aniss ?&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>&lt;slow&gt;Le sac attend, près des sandales. Le seau, le filet, et le linge. Tu prends quoi d'abord, Aniss ?&lt;/slow&gt; [long-pause]</t>
+          <t>&lt;slow&gt;Le sac attend, près des sandales. Le seau, le filet, et le linge. Aniss serre la coquille, puis la pose. Tu prends quoi d'abord, Aniss ?&lt;/slow&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr"/>
@@ -1561,6 +1565,7 @@
         <is>
           <t>narrateur|Le sac attend, près des sandales.
 narrateur|Le seau, le filet, et le linge.
+narrateur|Aniss serre la coquille, puis la pose.
 maman|Tu prends quoi d'abord, Aniss ?</t>
         </is>
       </c>
@@ -17516,7 +17521,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A16"/>
+  <dimension ref="A1:A17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -17629,6 +17634,13 @@
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>

--- a/stories/arbres/TREE-DIF-001.xlsx
+++ b/stories/arbres/TREE-DIF-001.xlsx
@@ -17521,7 +17521,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A17"/>
+  <dimension ref="A1:A18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -17641,6 +17641,13 @@
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
